--- a/10_Threshold_OUTPUT_REPORT/10_best_conclusion_data.xlsx
+++ b/10_Threshold_OUTPUT_REPORT/10_best_conclusion_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T69"/>
+  <dimension ref="A1:V69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,50 +481,60 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Execution Time (s)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Analysis Note</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>coords</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>length</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>full_pattern</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Inverted_Pval</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Alignment</t>
         </is>
@@ -579,40 +589,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/C1F978_Acidobacterium_capsulatum_ATCC_51196_direct_boot.png</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="n">
+        <v>0.4302</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3), (15, 4), (16, 5), (17, 6)]</t>
         </is>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>7</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>7.998179496224076</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>GCGAACA</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>GCGAAGA</t>
         </is>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>GCGAAGAAAAGGCGAACA</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
         <v>0.02299080367852859</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>0.9770091963214714</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -667,40 +685,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q9ZFA4_Acidobacterium_capsulatum_ATCC_51196_direct_boot.png</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>[(12, 1), (13, 2), (14, 3), (15, 4), (16, 5), (17, 6)]</t>
         </is>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>6</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>CGAACA</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>CGAACA</t>
         </is>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>CGAACAAAAACCGAACA</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
         <v>0.1105557776889244</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0.8894442223110756</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -755,40 +781,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q8UFK2_Agrobacterium_fabrum_str__C58_direct_boot.png</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="n">
+        <v>0.4488</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>[(11, 6), (12, 7), (13, 8), (14, 9), (15, 10)]</t>
         </is>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>5</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>9.999999948007035</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>TTGTT</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>TTGTT</t>
         </is>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>TTGTTTTGTT</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
         <v>0.6271491403438625</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>0.3728508596561375</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -843,40 +877,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/P31080_Bacillus_subtilis_subsp__subtilis_str__168_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0.2498</v>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>[(7, 6), (8, 5), (9, 4), (10, 3), (11, 2), (12, 1), (13, 0)]</t>
         </is>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>7</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>8.158871005219851</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>CGAACAT</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>ATGTTCG</t>
         </is>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>CGAACATATGTTCG</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -931,36 +973,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q6MHM9_Bdellovibrio_bacteriovorus_HD100_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>0.2785</v>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>[(8, 6), (9, 5), (10, 4), (11, 3), (12, 2)]</t>
         </is>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>5</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>8.877443704354082</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>TTACA</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>AGTAA</t>
         </is>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>TTACACAGTAA</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
         <v>0.06597361055577769</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>0.9340263894442223</v>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -1015,36 +1065,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q2SVP7_Burkholderia_thailandensis_E264_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>0.2547</v>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>[(12, 3), (13, 2), (14, 1), (15, 0)]</t>
         </is>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>4</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>7.1887218374957</v>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>CTGT</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>ACAG</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>CTGTTTTTTTATACAG</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
         <v>0.002798880447820872</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>0.9972011195521792</v>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1099,40 +1157,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/P0CAW8_Caulobacter_crescentus_CB15_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>( Caulobacter crescentus NA1000)</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>[(11, 4), (12, 3), (13, 2), (14, 1)]</t>
         </is>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>4</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>4.649439088043361</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>TAAC</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>TTAA</t>
         </is>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>TAACGCTCTGTTAA</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
         <v>0.03298680527788884</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>0.9670131947221111</v>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -1187,36 +1253,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q9A724_Caulobacter_crescentus_CB15_direct_boot.png</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>0.4953</v>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
         <is>
           <t>[(12, 1), (13, 2), (14, 3), (15, 4), (16, 5), (17, 6), (18, 7)]</t>
         </is>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>7</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>8.629871735080744</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>ATGTTCT</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>ATGTTCT</t>
         </is>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>ATGTTCTCGTTATGTTCT</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
         <v>0.0005997600959616154</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>0.9994002399040384</v>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1271,40 +1345,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/P0CAW8_Caulobacter_crescentus_NA1000_direct_boot.png</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="n">
+        <v>0.4514</v>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>( Caulobacter crescentus NA1000)</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
         <is>
           <t>[(12, 1), (13, 2), (14, 3), (15, 4), (16, 5)]</t>
         </is>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>5</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>5.644219182897489</v>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>TTAAC</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>TTAAT</t>
         </is>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>TTAATGTCCGGTTAAC</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
         <v>0.001599360255897641</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>0.9984006397441023</v>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1359,36 +1441,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/A0A072Z841_Corynebacterium_glutamicum_ATCC_13032_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>0.2651</v>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
         <is>
           <t>[(9, 6), (10, 5), (11, 4), (12, 3), (13, 2), (14, 1), (15, 0)]</t>
         </is>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>7</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>6.018460567146161</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>TCGAACA</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>TGTTCGA</t>
         </is>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>TCGAACATATGTTCGA</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1443,36 +1533,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q79VI7_Corynebacterium_glutamicum_ATCC_13032_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>0.5515</v>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
         <is>
           <t>[(15, 4), (16, 3), (17, 2), (18, 1)]</t>
         </is>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>4.574140548750501</v>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>TGAT</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>ATCA</t>
         </is>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>TGATTGTAACTTCGATCA</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
         <v>0.2542982806877249</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.745701719312275</v>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -1527,36 +1625,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q79VI7_Corynebacterium_glutamicum_R_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>0.2828</v>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
         <is>
           <t>[(10, 5), (11, 4), (12, 3), (13, 2), (14, 1), (15, 0)]</t>
         </is>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>6</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>5.088423751903059</v>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>TGTGAT</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>ATCACA</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>TGTGATCTACATCACA</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1611,40 +1717,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/P31080_Dehalococcoides_ethenogenes_195_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="n">
+        <v>0.1872</v>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
         <is>
           <t>[(8, 5), (9, 4), (10, 3), (11, 2), (12, 1), (13, 0)]</t>
         </is>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>6</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>AGAACA</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>TGTTCT</t>
         </is>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>AGAACAAGTGTTCT</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
         <v>0.005997600959616154</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>0.9940023990403839</v>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1699,40 +1813,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q3Z9S7_Dehalococcoides_ethenogenes_195_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="n">
+        <v>0.2217</v>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
         <is>
           <t>[(8, 5), (9, 4), (10, 3), (11, 2), (12, 1), (13, 0)]</t>
         </is>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>6</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>10.87744369395549</v>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>AGAACA</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>TGTTCT</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>AGAACAAATGTTCT</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
         <v>0.001399440223910436</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>0.9986005597760895</v>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1787,40 +1909,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/P0A7C2_Escherichia_coli_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" t="n">
+        <v>0.2741</v>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>[Escherichia coli str. K-12 substr. MG1655]</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
         <is>
           <t>[(14, 5), (15, 4), (16, 3), (17, 2), (18, 1), (19, 0)]</t>
         </is>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>6</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>GACTGT</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>ACAGTC</t>
         </is>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>GACTGTTTTTTTGTACAGTC</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1875,40 +2005,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/P0A7C2_Escherichia_coli_str__K-12_substr__MG1655_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>[Escherichia coli str. K-12 substr. MG1655]</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
         <is>
           <t>[(10, 9), (11, 8), (12, 7), (13, 6), (14, 5), (15, 4), (16, 3), (17, 2), (18, 1), (19, 0)]</t>
         </is>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>10</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>9.129186210109001</v>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>TACTGTATTT</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>ATATACAGTA</t>
         </is>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>TACTGTATTTATATACAGTA</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1963,36 +2101,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/P0A9E5_Escherichia_coli_str__K-12_substr__MG1655_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>0.7692</v>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
         <is>
           <t>[(13, 8), (14, 7), (15, 6), (16, 5), (17, 4), (18, 3), (19, 2), (20, 1), (21, 0)]</t>
         </is>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>9</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>7.868062409322926</v>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>TACATTGAG</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>ATCAAAAAA</t>
         </is>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>TACATTGAGCAGGATCAAAAAA</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2047,36 +2193,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/P0A9Q1_Escherichia_coli_str__K-12_substr__MG1655_direct_boot.png</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>0.5345</v>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3), (15, 4), (16, 5), (17, 6)]</t>
         </is>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>7</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>6.712915634015472</v>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>ATGTTAA</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>TTGTTAA</t>
         </is>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>TTGTTAAAAAAATGTTAA</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="S19" t="n">
+      <c r="U19" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2131,36 +2285,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/P0ACJ8_Escherichia_coli_str__K-12_substr__MG1655_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>0.4281</v>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
         <is>
           <t>[(14, 7), (15, 6), (16, 5), (17, 4), (18, 3)]</t>
         </is>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>5</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6.230875573321077</v>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>TGTGA</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>TCACA</t>
         </is>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>TGTGATCGATATCACA</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="S20" t="n">
+      <c r="U20" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2215,40 +2377,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/P23836_Escherichia_coli_str__K-12_substr__MG1655_direct_boot.png</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" t="n">
+        <v>0.9837</v>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>(Escherichia coli str. K-12 substr. W3110)</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
         <is>
           <t>[(13, 2), (14, 3), (15, 4), (16, 5), (17, 6), (18, 7), (19, 8), (20, 9), (21, 10)]</t>
         </is>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>9</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>6.471313798373604</v>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>TTGTTTATA</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>TTGTTTATA</t>
         </is>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>TTGTTTATATTTTGTTTATA</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
         <v>0.0009996001599360256</v>
       </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
         <v>0.9990003998400639</v>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2303,40 +2473,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/P23836_Escherichia_coli_str__K-12_substr__W3110_direct_boot.png</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>(Escherichia coli str. K-12 substr. W3110)</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3), (15, 4), (16, 5)]</t>
         </is>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>6</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>8.647947666979002</v>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>TGTTTA</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>TGTTTA</t>
         </is>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>TGTTTAGGGTTTGTTTA</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
         <v>0.01079568172730908</v>
       </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
         <v>0.989204318272691</v>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2391,40 +2569,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/P0DN68_Fibrobacter_succinogenes_subsp__succinogenes_S85_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" t="n">
+        <v>0.2639</v>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>(https://www.microbiologyresearch.org/content/journal/micro/10.1099/mic.0.27315-0)</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
         <is>
           <t>[(12, 3), (13, 2), (14, 1)]</t>
         </is>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>3</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>3.378825754835315</v>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>TGC</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>GCA</t>
         </is>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>TGCTCAAAGGGGCA</t>
+        </is>
+      </c>
+      <c r="T23" t="n">
         <v>0.1687325069972011</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
         <v>0.8312674930027989</v>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -2479,40 +2665,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/P61609_Geobacter_sulfurreducens_PCA_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
         <is>
           <t>[(9, 8), (10, 7), (11, 6), (12, 5), (13, 4), (14, 3), (15, 2), (16, 1), (17, 0)]</t>
         </is>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>9</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>13.50977493180085</v>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>GGTTGACAC</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>ATGTAAACC</t>
         </is>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>GGTTGACACATGTAAACC</t>
+        </is>
+      </c>
+      <c r="T24" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2567,36 +2761,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/P44858_Haemophilus_influenzae_Rd_KW20_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>0.3038</v>
+      </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
         <is>
           <t>[(10, 5), (11, 4), (12, 3), (13, 2), (14, 1), (15, 0)]</t>
         </is>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>6</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>7.630660794740063</v>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>CTGTAC</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>ATACAG</t>
         </is>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>CTGTACATCAATACAG</t>
+        </is>
+      </c>
+      <c r="T25" t="n">
         <v>0.002798880447820872</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>0.9972011195521792</v>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2651,36 +2853,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/P61611_Leptospira_interrogans_serovar_Copenhageni_str__Fiocruz_L1-130_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>0.2303</v>
+      </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
         <is>
           <t>[(10, 2), (11, 1), (12, 0)]</t>
         </is>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>3</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>4.845945699069486</v>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>TTT</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>TTTGAAATTCAAA</t>
+        </is>
+      </c>
+      <c r="T26" t="n">
         <v>0.04558176729308277</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>0.9544182327069173</v>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2735,40 +2945,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q8F663_Leptospira_interrogans_serovar_Lai_str__56601_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" t="n">
+        <v>0.2079</v>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
         <is>
           <t>[(9, 3), (10, 2), (11, 1), (12, 0)]</t>
         </is>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>4</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>7.999999958405628</v>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>TTTG</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>CAAA</t>
         </is>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>TTTGCTATACAAA</t>
+        </is>
+      </c>
+      <c r="T27" t="n">
         <v>0.2249100359856057</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>0.7750899640143942</v>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -2823,36 +3041,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q8Y7H7_Listeria_monocytogenes_EGD-e_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>0.4349</v>
+      </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
         <is>
           <t>[(11, 10), (12, 9), (13, 8), (14, 7), (15, 6), (16, 5), (17, 4)]</t>
         </is>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>7</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>8.825779900888758</v>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>AGAACAT</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>ATGTTCG</t>
         </is>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>AGAACATATGTTCG</t>
+        </is>
+      </c>
+      <c r="T28" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="S28" t="n">
+      <c r="U28" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2907,40 +3133,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/A0L9E2_Magnetococcus_marinus_MC-1_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K29" t="n">
+        <v>0.5033</v>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
         <is>
           <t>[(9, 8), (10, 7), (11, 6), (12, 5), (13, 4), (14, 3), (15, 2), (16, 1), (17, 0)]</t>
         </is>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>9</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>14.99999991741126</v>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>ACCTAATAA</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>AAATAAGGT</t>
         </is>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>ACCTAATAAAAATAAGGT</t>
+        </is>
+      </c>
+      <c r="T29" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2995,40 +3229,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/A0QVY5_Mycobacterium_leprae_TN_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" t="n">
+        <v>0.1614</v>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
         <is>
           <t>[(7, 4), (8, 3), (9, 2), (10, 1)]</t>
         </is>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>4</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>7.999999958405628</v>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>AACA</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>TGTT</t>
         </is>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>AACACATGTT</t>
+        </is>
+      </c>
+      <c r="T30" t="n">
         <v>0.1273490603758497</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.8726509396241503</v>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3083,40 +3325,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/A0QVY5_Mycobacterium_smegmatis_str__MC2_155_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" t="n">
+        <v>0.1906</v>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
         <is>
           <t>[(7, 4), (8, 3), (9, 2), (10, 1), (11, 0)]</t>
         </is>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>5</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>9.999999948007035</v>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>GAACA</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>TGTTC</t>
         </is>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>GAACAGGTGTTC</t>
+        </is>
+      </c>
+      <c r="T31" t="n">
         <v>0.00699720111955218</v>
       </c>
-      <c r="S31" t="n">
+      <c r="U31" t="n">
         <v>0.9930027988804478</v>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3171,40 +3421,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/A0QVY5_Mycobacterium_tuberculosis_H37Rv_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" t="n">
+        <v>0.2225</v>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
         <is>
           <t>[(9, 6), (10, 5), (11, 4), (12, 3), (13, 2), (14, 1)]</t>
         </is>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>6</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>CGAACA</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>TGTTCG</t>
         </is>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>CGAACAGGTGTTCG</t>
+        </is>
+      </c>
+      <c r="T32" t="n">
         <v>0.002399040383846461</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
         <v>0.9976009596161536</v>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3259,36 +3517,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/I6Y1J7_Mycobacterium_tuberculosis_H37Rv_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>0.332</v>
+      </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
         <is>
           <t>[(11, 8), (12, 7), (13, 6), (14, 5), (15, 4), (16, 3), (17, 2)]</t>
         </is>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>7</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>10.30104249561152</v>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>TCGAACA</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>TGTTCGA</t>
         </is>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>TCGAACACATGTTCGA</t>
+        </is>
+      </c>
+      <c r="T33" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="S33" t="n">
+      <c r="U33" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3343,36 +3609,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q1D406_Myxococcus_xanthus_DK_1622_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>0.2997</v>
+      </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
         <is>
           <t>[(9, 6), (10, 5), (11, 4), (12, 3)]</t>
         </is>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>4</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>4.632331227446766</v>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>AAAG</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>CGTT</t>
         </is>
       </c>
-      <c r="R34" t="n">
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>AAAGCCCGTT</t>
+        </is>
+      </c>
+      <c r="T34" t="n">
         <v>0.7978808476609356</v>
       </c>
-      <c r="S34" t="n">
+      <c r="U34" t="n">
         <v>0.2021191523390644</v>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3427,36 +3701,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/P0A4U6_Nostoc_sp__PCC_7120_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="n">
+        <v>0.3301</v>
+      </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
         <is>
           <t>[(8, 5), (9, 4), (10, 3), (11, 2), (12, 1), (13, 0)]</t>
         </is>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>6</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>4.649382099447238</v>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>GTATCA</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>TGATAC</t>
         </is>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>GTATCATATGATAC</t>
+        </is>
+      </c>
+      <c r="T35" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="S35" t="n">
+      <c r="U35" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3511,36 +3793,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q8YMM5_Nostoc_sp__PCC_7120_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="n">
+        <v>0.2485</v>
+      </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
         <is>
           <t>[(9, 6), (10, 5), (11, 4), (12, 3), (13, 2), (14, 1), (15, 0)]</t>
         </is>
       </c>
-      <c r="N36" t="n">
+      <c r="O36" t="n">
         <v>7</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>7.992602362854127</v>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>TAGTACT</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>TGTACTA</t>
         </is>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>TAGTACTTATGTACTA</t>
+        </is>
+      </c>
+      <c r="T36" t="n">
         <v>0.001999200319872051</v>
       </c>
-      <c r="S36" t="n">
+      <c r="U36" t="n">
         <v>0.998000799680128</v>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -3595,40 +3885,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/A1B3Z0_Paracoccus_denitrificans_PD1222_direct_boot.png</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K37" t="n">
+        <v>0.2548</v>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3)]</t>
         </is>
       </c>
-      <c r="N37" t="n">
+      <c r="O37" t="n">
         <v>4</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>7.999999958405628</v>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="R37" t="n">
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>GAACAACACAGGAAC</t>
+        </is>
+      </c>
+      <c r="T37" t="n">
         <v>0.06517393042782887</v>
       </c>
-      <c r="S37" t="n">
+      <c r="U37" t="n">
         <v>0.9348260695721711</v>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3683,36 +3981,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/P37452_Pseudomonas_aeruginosa_PAO1_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="n">
+        <v>0.3502</v>
+      </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
         <is>
           <t>[(12, 7), (13, 6), (14, 5), (15, 4), (16, 3), (17, 2), (18, 1)]</t>
         </is>
       </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
         <v>7</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>8.807992789210587</v>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>ACTGTAT</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>ATACAGT</t>
         </is>
       </c>
-      <c r="R38" t="n">
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>ACTGTATAAATATACAGT</t>
+        </is>
+      </c>
+      <c r="T38" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="S38" t="n">
+      <c r="U38" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3767,36 +4073,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q3K4G1_Pseudomonas_fluorescens_Pf0-1_direct_boot.png</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="n">
+        <v>0.5014</v>
+      </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3), (15, 4), (16, 5)]</t>
         </is>
       </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
         <v>6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>6.823397644601813</v>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>CTGTCA</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>CTGTCA</t>
         </is>
       </c>
-      <c r="R39" t="n">
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>CTGTCACACAACTGTCA</t>
+        </is>
+      </c>
+      <c r="T39" t="n">
         <v>0.002399040383846461</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>0.9976009596161536</v>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3851,36 +4165,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/P0A153_Pseudomonas_putida_KT2440_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="n">
+        <v>0.39</v>
+      </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
         <is>
           <t>[(11, 10), (12, 9), (13, 8), (14, 7), (15, 6), (16, 5), (17, 4), (18, 3)]</t>
         </is>
       </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>8</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>8.833999872781469</v>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>CTGGATAT</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>ATATACAG</t>
         </is>
       </c>
-      <c r="R40" t="n">
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>CTGGATATATATACAG</t>
+        </is>
+      </c>
+      <c r="T40" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="S40" t="n">
+      <c r="U40" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3935,36 +4257,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q88F34_Pseudomonas_putida_KT2440_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="n">
+        <v>0.4698</v>
+      </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
         <is>
           <t>[(8, 5), (9, 4), (10, 3), (11, 2), (12, 1), (13, 0)]</t>
         </is>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>6</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>8.111705777758363</v>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>TTGATC</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>GATCAA</t>
         </is>
       </c>
-      <c r="R41" t="n">
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>TTGATCCAGATCAA</t>
+        </is>
+      </c>
+      <c r="T41" t="n">
         <v>0.001799280287884846</v>
       </c>
-      <c r="S41" t="n">
+      <c r="U41" t="n">
         <v>0.9982007197121151</v>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4019,40 +4349,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q88PE9_Pseudomonas_putida_KT2440_direct_boot.png</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K42" t="n">
+        <v>0.2682</v>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>(https://pmc.ncbi.nlm.nih.gov/articles/PMC2689224/)</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
         <is>
           <t>[(8, 7), (9, 8), (10, 9), (11, 10), (12, 11)]</t>
         </is>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>5</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>9.553371688763029</v>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>TTTTT</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>TTTTT</t>
         </is>
       </c>
-      <c r="R42" t="n">
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>TTTTTT</t>
+        </is>
+      </c>
+      <c r="T42" t="n">
         <v>0.009996001599360257</v>
       </c>
-      <c r="S42" t="n">
+      <c r="U42" t="n">
         <v>0.9900039984006398</v>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4107,40 +4445,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q883X4_Pseudomonas_syringae_pv__tomato_str__DC3000_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K43" t="n">
+        <v>0.2579</v>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>(?? https://apsjournals.apsnet.org/doi/pdf/10.1094/MPMI-23-7-0927)</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
         <is>
           <t>[(10, 5), (11, 4), (12, 3), (13, 2), (14, 1), (15, 0)]</t>
         </is>
       </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
         <v>6</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>7.668638071329797</v>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>GTATCA</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>GGATAC</t>
         </is>
       </c>
-      <c r="R43" t="n">
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>GTATCACCCCGGATAC</t>
+        </is>
+      </c>
+      <c r="T43" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="S43" t="n">
+      <c r="U43" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4195,36 +4541,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/D5ALN0_Rhodobacter_capsulatus_SB_1003_direct_boot.png</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="n">
+        <v>0.2962</v>
+      </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3)]</t>
         </is>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>4</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>7.42297282353826</v>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="R44" t="n">
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>GAACAAGACCGGAAC</t>
+        </is>
+      </c>
+      <c r="T44" t="n">
         <v>0.005597760895641743</v>
       </c>
-      <c r="S44" t="n">
+      <c r="U44" t="n">
         <v>0.9944022391043582</v>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4279,40 +4633,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/C1F978_Rhodobacter_sphaeroides_2_4_1_direct_boot.png</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
         <is>
           <t>[(13, 2), (14, 3), (15, 4), (16, 5)]</t>
         </is>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>4</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>7.999999958405628</v>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="R45" t="n">
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>GAACACGCGCAGAAC</t>
+        </is>
+      </c>
+      <c r="T45" t="n">
         <v>0.1183526589364254</v>
       </c>
-      <c r="S45" t="n">
+      <c r="U45" t="n">
         <v>0.8816473410635746</v>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -4367,40 +4729,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q9ZFA4_Rhodobacter_sphaeroides_2_4_1_direct_boot.png</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K46" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3)]</t>
         </is>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
         <v>4</v>
       </c>
-      <c r="O46" t="n">
+      <c r="P46" t="n">
         <v>7.999999958405628</v>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="R46" t="n">
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>GAACACGCGCAGAAC</t>
+        </is>
+      </c>
+      <c r="T46" t="n">
         <v>0.07217113154738104</v>
       </c>
-      <c r="S46" t="n">
+      <c r="U46" t="n">
         <v>0.9278288684526189</v>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -4455,40 +4825,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q9ZFA4_Rhodobacter_sphaeroides_ATCC_17029_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K47" t="n">
+        <v>0.2208</v>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
         <is>
           <t>[(8, 6), (9, 5), (10, 4), (11, 3), (12, 2), (13, 1), (14, 0)]</t>
         </is>
       </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
         <v>7</v>
       </c>
-      <c r="O47" t="n">
+      <c r="P47" t="n">
         <v>8.877443698221686</v>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>GAACACA</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>GACGAAC</t>
         </is>
       </c>
-      <c r="R47" t="n">
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>GAACACAGGACGAAC</t>
+        </is>
+      </c>
+      <c r="T47" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="S47" t="n">
+      <c r="U47" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -4543,36 +4921,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/A4FQD5_Saccharopolyspora_erythraea_NRRL_2338_direct_boot.png</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="n">
+        <v>0.2695</v>
+      </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
         <is>
           <t>[(13, 2), (14, 3), (15, 4)]</t>
         </is>
       </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
         <v>3</v>
       </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
         <v>3.485881343809507</v>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="R48" t="n">
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>AACGCTCCCGAAAC</t>
+        </is>
+      </c>
+      <c r="T48" t="n">
         <v>0.01599360255897641</v>
       </c>
-      <c r="S48" t="n">
+      <c r="U48" t="n">
         <v>0.9840063974410236</v>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4627,36 +5013,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/P0DM78_Salmonella_enterica_subsp__enterica_serovar_Typhimurium_str__LT2_direct_boot.png</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="n">
+        <v>0.8658</v>
+      </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
         <is>
           <t>[(14, 3), (15, 4), (16, 5), (17, 6), (18, 7), (19, 8)]</t>
         </is>
       </c>
-      <c r="N49" t="n">
+      <c r="O49" t="n">
         <v>6</v>
       </c>
-      <c r="O49" t="n">
+      <c r="P49" t="n">
         <v>6.193444837545022</v>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>TGTTTA</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>TGTTTA</t>
         </is>
       </c>
-      <c r="R49" t="n">
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>TGTTTAGATTTTGTTTA</t>
+        </is>
+      </c>
+      <c r="T49" t="n">
         <v>0.0009996001599360256</v>
       </c>
-      <c r="S49" t="n">
+      <c r="U49" t="n">
         <v>0.9990003998400639</v>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4711,36 +5105,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q8EAB9_Shewanella_oneidensis_MR-1_direct_boot.png</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="n">
+        <v>0.2657</v>
+      </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3)]</t>
         </is>
       </c>
-      <c r="N50" t="n">
+      <c r="O50" t="n">
         <v>4</v>
       </c>
-      <c r="O50" t="n">
+      <c r="P50" t="n">
         <v>5.623842152666399</v>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>GTTA</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>GTTA</t>
         </is>
       </c>
-      <c r="R50" t="n">
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>GTTAATTAAATGTTA</t>
+        </is>
+      </c>
+      <c r="T50" t="n">
         <v>0.1047580967612955</v>
       </c>
-      <c r="S50" t="n">
+      <c r="U50" t="n">
         <v>0.8952419032387046</v>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -4795,36 +5197,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q8EHJ3_Shewanella_oneidensis_MR-1_direct_boot.png</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="n">
+        <v>0.2626</v>
+      </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
         <is>
           <t>[(10, 0), (11, 1), (12, 2), (13, 3), (14, 4), (15, 5)]</t>
         </is>
       </c>
-      <c r="N51" t="n">
+      <c r="O51" t="n">
         <v>6</v>
       </c>
-      <c r="O51" t="n">
+      <c r="P51" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>TTCATA</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>TTCATA</t>
         </is>
       </c>
-      <c r="R51" t="n">
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>TTCATAATTTTTCATA</t>
+        </is>
+      </c>
+      <c r="T51" t="n">
         <v>0.006197520991603359</v>
       </c>
-      <c r="S51" t="n">
+      <c r="U51" t="n">
         <v>0.9938024790083967</v>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4879,36 +5289,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q92PW3_Sinorhizobium_meliloti_1021_direct_boot.png</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="n">
+        <v>0.4901</v>
+      </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
         <is>
           <t>[(12, 1), (13, 2), (14, 3), (15, 4), (16, 5)]</t>
         </is>
       </c>
-      <c r="N52" t="n">
+      <c r="O52" t="n">
         <v>5</v>
       </c>
-      <c r="O52" t="n">
+      <c r="P52" t="n">
         <v>7.938653979572283</v>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>TGTTC</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>TGTTC</t>
         </is>
       </c>
-      <c r="R52" t="n">
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>TGTTCTTGATTTGTTC</t>
+        </is>
+      </c>
+      <c r="T52" t="n">
         <v>0.02019192323070772</v>
       </c>
-      <c r="S52" t="n">
+      <c r="U52" t="n">
         <v>0.9798080767692923</v>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4963,36 +5381,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q9L4P1_Staphylococcus_aureus_subsp__aureus_COL_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="n">
+        <v>0.2155</v>
+      </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
         <is>
           <t>[(7, 6), (8, 5), (9, 4), (10, 3), (11, 2), (12, 1), (13, 0)]</t>
         </is>
       </c>
-      <c r="N53" t="n">
+      <c r="O53" t="n">
         <v>7</v>
       </c>
-      <c r="O53" t="n">
+      <c r="P53" t="n">
         <v>8.995593924090324</v>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>CGAACAT</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>ATGTTCG</t>
         </is>
       </c>
-      <c r="R53" t="n">
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>CGAACATATGTTCG</t>
+        </is>
+      </c>
+      <c r="T53" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="S53" t="n">
+      <c r="U53" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="V53" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5047,36 +5473,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/P74171_Synechocystis_sp__PCC_6803_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="n">
+        <v>0.2677</v>
+      </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
         <is>
           <t>[(10, 5), (11, 4), (12, 3), (13, 2), (14, 1), (15, 0)]</t>
         </is>
       </c>
-      <c r="N54" t="n">
+      <c r="O54" t="n">
         <v>6</v>
       </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
         <v>10.31820609521862</v>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>TGTGAT</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>ATCACA</t>
         </is>
       </c>
-      <c r="R54" t="n">
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>TGTGATCAAGATCACA</t>
+        </is>
+      </c>
+      <c r="T54" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="S54" t="n">
+      <c r="U54" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="V54" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5131,36 +5565,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q9KNW6_Vibrio_cholerae_O1_biovar_El_Tor_str__N16961_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="n">
+        <v>0.5832000000000001</v>
+      </c>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
         <is>
           <t>[(13, 8), (14, 7), (15, 6), (16, 5), (17, 4)]</t>
         </is>
       </c>
-      <c r="N55" t="n">
+      <c r="O55" t="n">
         <v>5</v>
       </c>
-      <c r="O55" t="n">
+      <c r="P55" t="n">
         <v>5.946157237883602</v>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>GTGAC</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>ATCAC</t>
         </is>
       </c>
-      <c r="R55" t="n">
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>GTGACATAGATCAC</t>
+        </is>
+      </c>
+      <c r="T55" t="n">
         <v>0.007796881247501</v>
       </c>
-      <c r="S55" t="n">
+      <c r="U55" t="n">
         <v>0.992203118752499</v>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5215,36 +5657,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q87KN2_Vibrio_parahaemolyticus_RIMD_2210633_direct_boot.png</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="n">
+        <v>0.4984</v>
+      </c>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
         <is>
           <t>[(6, 4), (7, 5), (8, 6), (9, 7), (10, 8), (11, 9), (12, 10), (13, 11), (14, 12), (15, 13)]</t>
         </is>
       </c>
-      <c r="N56" t="n">
+      <c r="O56" t="n">
         <v>10</v>
       </c>
-      <c r="O56" t="n">
+      <c r="P56" t="n">
         <v>9.193695773286672</v>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>TATAAATAAA</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>TGTATAAATA</t>
         </is>
       </c>
-      <c r="R56" t="n">
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>TGTATAAATAAA</t>
+        </is>
+      </c>
+      <c r="T56" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="S56" t="n">
+      <c r="U56" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -5299,36 +5749,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q7M7I9_Vibrio_vulnificus_CMCP6_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="n">
+        <v>0.372</v>
+      </c>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
         <is>
           <t>[(12, 3), (13, 2), (14, 1)]</t>
         </is>
       </c>
-      <c r="N57" t="n">
+      <c r="O57" t="n">
         <v>3</v>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
         <v>5.999999968804222</v>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>GTG</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>CAC</t>
         </is>
       </c>
-      <c r="R57" t="n">
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>GTGCGCCAAATCAC</t>
+        </is>
+      </c>
+      <c r="T57" t="n">
         <v>0.5715713714514195</v>
       </c>
-      <c r="S57" t="n">
+      <c r="U57" t="n">
         <v>0.4284286285485805</v>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="V57" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -5383,36 +5841,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q7M7I9_Vibrio_vulnificus_MO6-24_O_direct_boot.png</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="n">
+        <v>0.2207</v>
+      </c>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
         <is>
           <t>[(10, 6), (11, 7), (12, 8)]</t>
         </is>
       </c>
-      <c r="N58" t="n">
+      <c r="O58" t="n">
         <v>3</v>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
         <v>5.999999968804222</v>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>ATC</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>ATC</t>
         </is>
       </c>
-      <c r="R58" t="n">
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>ATCAATC</t>
+        </is>
+      </c>
+      <c r="T58" t="n">
         <v>0.5983606557377049</v>
       </c>
-      <c r="S58" t="n">
+      <c r="U58" t="n">
         <v>0.4016393442622951</v>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="V58" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -5467,36 +5933,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q7M7I9_Vibrio_vulnificus_YJ016_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="n">
+        <v>0.8736</v>
+      </c>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
         <is>
           <t>[(17, 10), (18, 9), (19, 8), (20, 7)]</t>
         </is>
       </c>
-      <c r="N59" t="n">
+      <c r="O59" t="n">
         <v>4</v>
       </c>
-      <c r="O59" t="n">
+      <c r="P59" t="n">
         <v>1.853855035407096</v>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>TGAT</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>CACA</t>
         </is>
       </c>
-      <c r="R59" t="n">
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>TGATCACTATCACA</t>
+        </is>
+      </c>
+      <c r="T59" t="n">
         <v>0.632546981207517</v>
       </c>
-      <c r="S59" t="n">
+      <c r="U59" t="n">
         <v>0.367453018792483</v>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="V59" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -5551,40 +6025,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q8PN77_Xanthomonas_axonopodis_pv__citri_str__306_direct_boot.png</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K60" t="n">
+        <v>0.1845</v>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
         <is>
           <t>[(8, 0), (9, 1), (10, 2), (11, 3), (12, 4), (13, 5)]</t>
         </is>
       </c>
-      <c r="N60" t="n">
+      <c r="O60" t="n">
         <v>6</v>
       </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>TGTACA</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>TGTACA</t>
         </is>
       </c>
-      <c r="R60" t="n">
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>TGTACAAATGTACA</t>
+        </is>
+      </c>
+      <c r="T60" t="n">
         <v>0.003798480607756897</v>
       </c>
-      <c r="S60" t="n">
+      <c r="U60" t="n">
         <v>0.9962015193922431</v>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -5639,36 +6121,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q4UZF6_Xanthomonas_campestris_pv__campestris_str__8004_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="n">
+        <v>0.3529</v>
+      </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
         <is>
           <t>[(15, 8), (16, 7), (17, 6), (18, 5), (19, 4), (20, 3)]</t>
         </is>
       </c>
-      <c r="N61" t="n">
+      <c r="O61" t="n">
         <v>6</v>
       </c>
-      <c r="O61" t="n">
+      <c r="P61" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>GGTGCG</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>CGCACC</t>
         </is>
       </c>
-      <c r="R61" t="n">
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>GGTGCGCTTCACCGCACC</t>
+        </is>
+      </c>
+      <c r="T61" t="n">
         <v>0.01239504198320672</v>
       </c>
-      <c r="S61" t="n">
+      <c r="U61" t="n">
         <v>0.9876049580167933</v>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="V61" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5723,36 +6213,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q4UZF6_Xanthomonas_campestris_pv__campestris_str__ATCC_33913_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="n">
+        <v>0.4874</v>
+      </c>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
         <is>
           <t>[(14, 7), (15, 6), (16, 5), (17, 4), (18, 3)]</t>
         </is>
       </c>
-      <c r="N62" t="n">
+      <c r="O62" t="n">
         <v>5</v>
       </c>
-      <c r="O62" t="n">
+      <c r="P62" t="n">
         <v>4.559670595665593</v>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>TGTGA</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>CCACA</t>
         </is>
       </c>
-      <c r="R62" t="n">
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>TGTGAACCTCCCCACA</t>
+        </is>
+      </c>
+      <c r="T62" t="n">
         <v>0.001999200319872051</v>
       </c>
-      <c r="S62" t="n">
+      <c r="U62" t="n">
         <v>0.998000799680128</v>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="V62" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5807,40 +6305,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q9PH24_Xylella_fastidiosa_9a5c_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="K63" t="n">
+        <v>0.2345</v>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
         <is>
           <t>[(10, 5), (11, 4), (12, 3), (13, 2), (14, 1), (15, 0)]</t>
         </is>
       </c>
-      <c r="N63" t="n">
+      <c r="O63" t="n">
         <v>6</v>
       </c>
-      <c r="O63" t="n">
+      <c r="P63" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>TTAGTA</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>TACTAA</t>
         </is>
       </c>
-      <c r="R63" t="n">
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>TTAGTAAAAATACTAA</t>
+        </is>
+      </c>
+      <c r="T63" t="n">
         <v>0.001399440223910436</v>
       </c>
-      <c r="S63" t="n">
+      <c r="U63" t="n">
         <v>0.9986005597760895</v>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="V63" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5895,40 +6401,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/A0A0B6P4W3_Yersinia_pestis_CO92_direct_boot.png</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="K64" t="n">
+        <v>0.4838</v>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t>(Yersinia pestis KIM10+)</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3), (15, 4), (16, 5), (17, 6)]</t>
         </is>
       </c>
-      <c r="N64" t="n">
+      <c r="O64" t="n">
         <v>7</v>
       </c>
-      <c r="O64" t="n">
+      <c r="P64" t="n">
         <v>4.956461640427081</v>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>TGTTTAT</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>TGTTTAA</t>
         </is>
       </c>
-      <c r="R64" t="n">
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>TGTTTAATTATTGTTTAT</t>
+        </is>
+      </c>
+      <c r="T64" t="n">
         <v>0.01739304278288685</v>
       </c>
-      <c r="S64" t="n">
+      <c r="U64" t="n">
         <v>0.9826069572171131</v>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="V64" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5983,36 +6497,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q7CFV3_Yersinia_pestis_CO92_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="n">
+        <v>0.5219</v>
+      </c>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
         <is>
           <t>[(14, 9), (15, 8), (16, 7), (17, 6), (18, 5), (19, 4)]</t>
         </is>
       </c>
-      <c r="N65" t="n">
+      <c r="O65" t="n">
         <v>6</v>
       </c>
-      <c r="O65" t="n">
+      <c r="P65" t="n">
         <v>6.726153901717278</v>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>TGTGAT</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>ATCACA</t>
         </is>
       </c>
-      <c r="R65" t="n">
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>TGTGATTTAGATCACA</t>
+        </is>
+      </c>
+      <c r="T65" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="S65" t="n">
+      <c r="U65" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="V65" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6067,40 +6589,48 @@
           <t>10_Threshold_OUTPUT_REPORT/images/A0A0B6P4W3_Yersinia_pestis_KIM10__direct_boot.png</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="K66" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t>(Yersinia pestis KIM10+)</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3), (15, 4), (16, 5), (17, 6)]</t>
         </is>
       </c>
-      <c r="N66" t="n">
+      <c r="O66" t="n">
         <v>7</v>
       </c>
-      <c r="O66" t="n">
+      <c r="P66" t="n">
         <v>6.725409521382448</v>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>TTGTTTA</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>CTGTTTA</t>
         </is>
       </c>
-      <c r="R66" t="n">
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>CTGTTTATAATTTGTTTA</t>
+        </is>
+      </c>
+      <c r="T66" t="n">
         <v>0.001799280287884846</v>
       </c>
-      <c r="S66" t="n">
+      <c r="U66" t="n">
         <v>0.9982007197121151</v>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="V66" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6155,36 +6685,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q7CFV3_Yersinia_pestis_biovar_Microtus_str__91001_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="n">
+        <v>2.2486</v>
+      </c>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
         <is>
           <t>[(14, 4), (15, 3), (16, 2)]</t>
         </is>
       </c>
-      <c r="N67" t="n">
+      <c r="O67" t="n">
         <v>3</v>
       </c>
-      <c r="O67" t="n">
+      <c r="P67" t="n">
         <v>5.999999968804222</v>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>CAA</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>TTG</t>
         </is>
       </c>
-      <c r="R67" t="n">
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>CAAGGTGTTAGATTG</t>
+        </is>
+      </c>
+      <c r="T67" t="n">
         <v>0.9948020791683326</v>
       </c>
-      <c r="S67" t="n">
+      <c r="U67" t="n">
         <v>0.005197920831667369</v>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="V67" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -6239,36 +6777,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q7CFX0_Yersinia_pestis_biovar_Microtus_str__91001_direct_boot.png</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="n">
+        <v>0.6098</v>
+      </c>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
         <is>
           <t>[(11, 1), (12, 2), (13, 3), (14, 4), (15, 5), (16, 6), (17, 7), (18, 8)]</t>
         </is>
       </c>
-      <c r="N68" t="n">
+      <c r="O68" t="n">
         <v>8</v>
       </c>
-      <c r="O68" t="n">
+      <c r="P68" t="n">
         <v>5.432587976962286</v>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>TAACATTT</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>ATACACTT</t>
         </is>
       </c>
-      <c r="R68" t="n">
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>ATACACTTTGTAACATTT</t>
+        </is>
+      </c>
+      <c r="T68" t="n">
         <v>0.04838064774090364</v>
       </c>
-      <c r="S68" t="n">
+      <c r="U68" t="n">
         <v>0.9516193522590963</v>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="V68" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6323,36 +6869,44 @@
           <t>10_Threshold_OUTPUT_REPORT/images/Q7CFX0_Yersinia_pseudotuberculosis_YPIII_reverse_boot.png</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="n">
+        <v>0.6469</v>
+      </c>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
         <is>
           <t>[(14, 12), (15, 11), (16, 10), (17, 9), (18, 8)]</t>
         </is>
       </c>
-      <c r="N69" t="n">
+      <c r="O69" t="n">
         <v>5</v>
       </c>
-      <c r="O69" t="n">
+      <c r="P69" t="n">
         <v>6.877443711686477</v>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>CAAAA</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>GTTAA</t>
         </is>
       </c>
-      <c r="R69" t="n">
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>CAAAATGTTAA</t>
+        </is>
+      </c>
+      <c r="T69" t="n">
         <v>0.2990803678528589</v>
       </c>
-      <c r="S69" t="n">
+      <c r="U69" t="n">
         <v>0.7009196321471411</v>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="V69" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>

--- a/10_Threshold_OUTPUT_REPORT/10_best_conclusion_data.xlsx
+++ b/10_Threshold_OUTPUT_REPORT/10_best_conclusion_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V69"/>
+  <dimension ref="A1:W69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,15 +526,20 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>evaluation</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Inverted_Pval</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Alignment</t>
         </is>
@@ -590,7 +595,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.4302</v>
+        <v>0.4695</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -624,13 +629,18 @@
           <t>GCGAAGAAAAGGCGAACA</t>
         </is>
       </c>
-      <c r="T2" t="n">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
         <v>0.02299080367852859</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>0.9770091963214714</v>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -686,7 +696,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.3584</v>
+        <v>0.4081</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -720,13 +730,18 @@
           <t>CGAACAAAAACCGAACA</t>
         </is>
       </c>
-      <c r="T3" t="n">
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
         <v>0.1105557776889244</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>0.8894442223110756</v>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -782,7 +797,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.4488</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -816,13 +831,18 @@
           <t>TTGTTTTGTT</t>
         </is>
       </c>
-      <c r="T4" t="n">
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
         <v>0.6271491403438625</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>0.3728508596561375</v>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -878,7 +898,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.2498</v>
+        <v>0.2979</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -912,13 +932,18 @@
           <t>CGAACATATGTTCG</t>
         </is>
       </c>
-      <c r="T5" t="n">
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -974,7 +999,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.2785</v>
+        <v>0.3392</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -1004,13 +1029,18 @@
           <t>TTACACAGTAA</t>
         </is>
       </c>
-      <c r="T6" t="n">
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
         <v>0.06597361055577769</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>0.9340263894442223</v>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -1066,7 +1096,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.2547</v>
+        <v>0.2653</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -1096,13 +1126,18 @@
           <t>CTGTTTTTTTATACAG</t>
         </is>
       </c>
-      <c r="T7" t="n">
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
         <v>0.002798880447820872</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>0.9972011195521792</v>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1158,7 +1193,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.2899</v>
+        <v>0.3044</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1192,13 +1227,18 @@
           <t>TAACGCTCTGTTAA</t>
         </is>
       </c>
-      <c r="T8" t="n">
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
         <v>0.03298680527788884</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>0.9670131947221111</v>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -1254,7 +1294,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.4953</v>
+        <v>0.507</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -1284,13 +1324,18 @@
           <t>ATGTTCTCGTTATGTTCT</t>
         </is>
       </c>
-      <c r="T9" t="n">
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
         <v>0.0005997600959616154</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>0.9994002399040384</v>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1346,7 +1391,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.4514</v>
+        <v>0.5179</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1380,13 +1425,18 @@
           <t>TTAATGTCCGGTTAAC</t>
         </is>
       </c>
-      <c r="T10" t="n">
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
         <v>0.001599360255897641</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>0.9984006397441023</v>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1442,7 +1492,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0.2651</v>
+        <v>0.2588</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
@@ -1472,13 +1522,18 @@
           <t>TCGAACATATGTTCGA</t>
         </is>
       </c>
-      <c r="T11" t="n">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1534,7 +1589,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0.5515</v>
+        <v>0.6046</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
@@ -1564,13 +1619,18 @@
           <t>TGATTGTAACTTCGATCA</t>
         </is>
       </c>
-      <c r="T12" t="n">
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
         <v>0.2542982806877249</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>0.745701719312275</v>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -1626,7 +1686,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0.2828</v>
+        <v>0.343</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
@@ -1656,13 +1716,18 @@
           <t>TGTGATCTACATCACA</t>
         </is>
       </c>
-      <c r="T13" t="n">
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1718,7 +1783,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.1872</v>
+        <v>0.2083</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1752,13 +1817,18 @@
           <t>AGAACAAGTGTTCT</t>
         </is>
       </c>
-      <c r="T14" t="n">
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
         <v>0.005997600959616154</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>0.9940023990403839</v>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1814,7 +1884,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.2217</v>
+        <v>0.2415</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1848,13 +1918,18 @@
           <t>AGAACAAATGTTCT</t>
         </is>
       </c>
-      <c r="T15" t="n">
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
         <v>0.001399440223910436</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>0.9986005597760895</v>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1910,7 +1985,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0.2741</v>
+        <v>0.3305</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1944,13 +2019,18 @@
           <t>GACTGTTTTTTTGTACAGTC</t>
         </is>
       </c>
-      <c r="T16" t="n">
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2006,7 +2086,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0.3881</v>
+        <v>0.3921</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -2040,13 +2120,18 @@
           <t>TACTGTATTTATATACAGTA</t>
         </is>
       </c>
-      <c r="T17" t="n">
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2102,7 +2187,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0.7692</v>
+        <v>0.7024</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
@@ -2132,13 +2217,18 @@
           <t>TACATTGAGCAGGATCAAAAAA</t>
         </is>
       </c>
-      <c r="T18" t="n">
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2194,7 +2284,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0.5345</v>
+        <v>0.6017</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
@@ -2224,13 +2314,18 @@
           <t>TTGTTAAAAAAATGTTAA</t>
         </is>
       </c>
-      <c r="T19" t="n">
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2286,7 +2381,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0.4281</v>
+        <v>0.4949</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
@@ -2316,13 +2411,18 @@
           <t>TGTGATCGATATCACA</t>
         </is>
       </c>
-      <c r="T20" t="n">
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2378,7 +2478,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>0.9837</v>
+        <v>0.9575</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2412,13 +2512,18 @@
           <t>TTGTTTATATTTTGTTTATA</t>
         </is>
       </c>
-      <c r="T21" t="n">
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
         <v>0.0009996001599360256</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>0.9990003998400639</v>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2474,7 +2579,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>0.4245</v>
+        <v>0.4293</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -2508,13 +2613,18 @@
           <t>TGTTTAGGGTTTGTTTA</t>
         </is>
       </c>
-      <c r="T22" t="n">
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
         <v>0.01079568172730908</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>0.989204318272691</v>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2570,7 +2680,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>0.2639</v>
+        <v>0.3208</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2604,13 +2714,18 @@
           <t>TGCTCAAAGGGGCA</t>
         </is>
       </c>
-      <c r="T23" t="n">
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U23" t="n">
         <v>0.1687325069972011</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>0.8312674930027989</v>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -2666,7 +2781,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>0.3042</v>
+        <v>0.3186</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -2700,13 +2815,18 @@
           <t>GGTTGACACATGTAAACC</t>
         </is>
       </c>
-      <c r="T24" t="n">
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U24" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2762,7 +2882,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>0.3038</v>
+        <v>0.3016</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
@@ -2792,13 +2912,18 @@
           <t>CTGTACATCAATACAG</t>
         </is>
       </c>
-      <c r="T25" t="n">
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U25" t="n">
         <v>0.002798880447820872</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>0.9972011195521792</v>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2854,7 +2979,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>0.2303</v>
+        <v>0.2934</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
@@ -2884,13 +3009,18 @@
           <t>TTTGAAATTCAAA</t>
         </is>
       </c>
-      <c r="T26" t="n">
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U26" t="n">
         <v>0.04558176729308277</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>0.9544182327069173</v>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2946,7 +3076,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>0.2079</v>
+        <v>0.2508</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2980,13 +3110,18 @@
           <t>TTTGCTATACAAA</t>
         </is>
       </c>
-      <c r="T27" t="n">
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U27" t="n">
         <v>0.2249100359856057</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>0.7750899640143942</v>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3042,7 +3177,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0.4349</v>
+        <v>0.453</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
@@ -3072,13 +3207,18 @@
           <t>AGAACATATGTTCG</t>
         </is>
       </c>
-      <c r="T28" t="n">
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U28" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3134,7 +3274,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>0.5033</v>
+        <v>0.507</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -3168,13 +3308,18 @@
           <t>ACCTAATAAAAATAAGGT</t>
         </is>
       </c>
-      <c r="T29" t="n">
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3230,7 +3375,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0.1614</v>
+        <v>0.1819</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -3264,13 +3409,18 @@
           <t>AACACATGTT</t>
         </is>
       </c>
-      <c r="T30" t="n">
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
         <v>0.1273490603758497</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>0.8726509396241503</v>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3326,7 +3476,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0.1906</v>
+        <v>0.2188</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -3360,13 +3510,18 @@
           <t>GAACAGGTGTTC</t>
         </is>
       </c>
-      <c r="T31" t="n">
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U31" t="n">
         <v>0.00699720111955218</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>0.9930027988804478</v>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3422,7 +3577,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>0.2225</v>
+        <v>0.2293</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -3456,13 +3611,18 @@
           <t>CGAACAGGTGTTCG</t>
         </is>
       </c>
-      <c r="T32" t="n">
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U32" t="n">
         <v>0.002399040383846461</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>0.9976009596161536</v>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3518,7 +3678,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>0.332</v>
+        <v>0.3732</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
@@ -3548,13 +3708,18 @@
           <t>TCGAACACATGTTCGA</t>
         </is>
       </c>
-      <c r="T33" t="n">
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U33" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3610,7 +3775,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>0.2997</v>
+        <v>0.3059</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -3640,13 +3805,18 @@
           <t>AAAGCCCGTT</t>
         </is>
       </c>
-      <c r="T34" t="n">
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U34" t="n">
         <v>0.7978808476609356</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>0.2021191523390644</v>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3702,7 +3872,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>0.3301</v>
+        <v>0.2857</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
@@ -3732,13 +3902,18 @@
           <t>GTATCATATGATAC</t>
         </is>
       </c>
-      <c r="T35" t="n">
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U35" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3794,7 +3969,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>0.2485</v>
+        <v>0.2591</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -3824,13 +3999,18 @@
           <t>TAGTACTTATGTACTA</t>
         </is>
       </c>
-      <c r="T36" t="n">
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U36" t="n">
         <v>0.001999200319872051</v>
       </c>
-      <c r="U36" t="n">
+      <c r="V36" t="n">
         <v>0.998000799680128</v>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -3886,7 +4066,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0.2548</v>
+        <v>0.3076</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -3920,13 +4100,18 @@
           <t>GAACAACACAGGAAC</t>
         </is>
       </c>
-      <c r="T37" t="n">
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U37" t="n">
         <v>0.06517393042782887</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>0.9348260695721711</v>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3982,7 +4167,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0.3502</v>
+        <v>0.3632</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
@@ -4012,13 +4197,18 @@
           <t>ACTGTATAAATATACAGT</t>
         </is>
       </c>
-      <c r="T38" t="n">
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U38" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U38" t="n">
+      <c r="V38" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4074,7 +4264,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0.5014</v>
+        <v>0.497</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
@@ -4104,13 +4294,18 @@
           <t>CTGTCACACAACTGTCA</t>
         </is>
       </c>
-      <c r="T39" t="n">
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U39" t="n">
         <v>0.002399040383846461</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>0.9976009596161536</v>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4166,7 +4361,7 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0.39</v>
+        <v>0.4527</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
@@ -4196,13 +4391,18 @@
           <t>CTGGATATATATACAG</t>
         </is>
       </c>
-      <c r="T40" t="n">
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U40" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4258,7 +4458,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0.4698</v>
+        <v>0.2489</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
@@ -4288,13 +4488,18 @@
           <t>TTGATCCAGATCAA</t>
         </is>
       </c>
-      <c r="T41" t="n">
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U41" t="n">
         <v>0.001799280287884846</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>0.9982007197121151</v>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4350,7 +4555,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>0.2682</v>
+        <v>0.3336</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -4384,13 +4589,18 @@
           <t>TTTTTT</t>
         </is>
       </c>
-      <c r="T42" t="n">
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U42" t="n">
         <v>0.009996001599360257</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>0.9900039984006398</v>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4446,7 +4656,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0.2579</v>
+        <v>0.2659</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -4480,13 +4690,18 @@
           <t>GTATCACCCCGGATAC</t>
         </is>
       </c>
-      <c r="T43" t="n">
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U43" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4542,7 +4757,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>0.2962</v>
+        <v>0.2805</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
@@ -4572,13 +4787,18 @@
           <t>GAACAAGACCGGAAC</t>
         </is>
       </c>
-      <c r="T44" t="n">
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U44" t="n">
         <v>0.005597760895641743</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>0.9944022391043582</v>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4634,7 +4854,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>0.543</v>
+        <v>0.5569</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -4668,13 +4888,18 @@
           <t>GAACACGCGCAGAAC</t>
         </is>
       </c>
-      <c r="T45" t="n">
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U45" t="n">
         <v>0.1183526589364254</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>0.8816473410635746</v>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -4730,7 +4955,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>0.2964</v>
+        <v>0.3507</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -4764,13 +4989,18 @@
           <t>GAACACGCGCAGAAC</t>
         </is>
       </c>
-      <c r="T46" t="n">
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U46" t="n">
         <v>0.07217113154738104</v>
       </c>
-      <c r="U46" t="n">
+      <c r="V46" t="n">
         <v>0.9278288684526189</v>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -4826,7 +5056,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>0.2208</v>
+        <v>0.2848</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -4860,13 +5090,18 @@
           <t>GAACACAGGACGAAC</t>
         </is>
       </c>
-      <c r="T47" t="n">
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U47" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U47" t="n">
+      <c r="V47" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -4922,7 +5157,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0.2695</v>
+        <v>0.2834</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
@@ -4952,13 +5187,18 @@
           <t>AACGCTCCCGAAAC</t>
         </is>
       </c>
-      <c r="T48" t="n">
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U48" t="n">
         <v>0.01599360255897641</v>
       </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
         <v>0.9840063974410236</v>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5014,7 +5254,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>0.8658</v>
+        <v>0.8998</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
@@ -5044,13 +5284,18 @@
           <t>TGTTTAGATTTTGTTTA</t>
         </is>
       </c>
-      <c r="T49" t="n">
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U49" t="n">
         <v>0.0009996001599360256</v>
       </c>
-      <c r="U49" t="n">
+      <c r="V49" t="n">
         <v>0.9990003998400639</v>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5106,7 +5351,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>0.2657</v>
+        <v>0.283</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
@@ -5136,13 +5381,18 @@
           <t>GTTAATTAAATGTTA</t>
         </is>
       </c>
-      <c r="T50" t="n">
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U50" t="n">
         <v>0.1047580967612955</v>
       </c>
-      <c r="U50" t="n">
+      <c r="V50" t="n">
         <v>0.8952419032387046</v>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -5198,7 +5448,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>0.2626</v>
+        <v>0.2823</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
@@ -5228,13 +5478,18 @@
           <t>TTCATAATTTTTCATA</t>
         </is>
       </c>
-      <c r="T51" t="n">
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U51" t="n">
         <v>0.006197520991603359</v>
       </c>
-      <c r="U51" t="n">
+      <c r="V51" t="n">
         <v>0.9938024790083967</v>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5290,7 +5545,7 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>0.4901</v>
+        <v>0.5108</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
@@ -5320,13 +5575,18 @@
           <t>TGTTCTTGATTTGTTC</t>
         </is>
       </c>
-      <c r="T52" t="n">
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U52" t="n">
         <v>0.02019192323070772</v>
       </c>
-      <c r="U52" t="n">
+      <c r="V52" t="n">
         <v>0.9798080767692923</v>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5382,7 +5642,7 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>0.2155</v>
+        <v>0.2362</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
@@ -5412,13 +5672,18 @@
           <t>CGAACATATGTTCG</t>
         </is>
       </c>
-      <c r="T53" t="n">
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U53" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U53" t="n">
+      <c r="V53" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5474,7 +5739,7 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>0.2677</v>
+        <v>0.2589</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
@@ -5504,13 +5769,18 @@
           <t>TGTGATCAAGATCACA</t>
         </is>
       </c>
-      <c r="T54" t="n">
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U54" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U54" t="n">
+      <c r="V54" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5566,7 +5836,7 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.6059</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
@@ -5596,13 +5866,18 @@
           <t>GTGACATAGATCAC</t>
         </is>
       </c>
-      <c r="T55" t="n">
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U55" t="n">
         <v>0.007796881247501</v>
       </c>
-      <c r="U55" t="n">
+      <c r="V55" t="n">
         <v>0.992203118752499</v>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5658,7 +5933,7 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>0.4984</v>
+        <v>0.5124</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
@@ -5688,13 +5963,18 @@
           <t>TGTATAAATAAA</t>
         </is>
       </c>
-      <c r="T56" t="n">
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
+      <c r="U56" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="U56" t="n">
+      <c r="V56" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -5750,7 +6030,7 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>0.372</v>
+        <v>0.3152</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
@@ -5780,13 +6060,18 @@
           <t>GTGCGCCAAATCAC</t>
         </is>
       </c>
-      <c r="T57" t="n">
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U57" t="n">
         <v>0.5715713714514195</v>
       </c>
-      <c r="U57" t="n">
+      <c r="V57" t="n">
         <v>0.4284286285485805</v>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -5842,7 +6127,7 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>0.2207</v>
+        <v>0.2264</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
@@ -5872,13 +6157,18 @@
           <t>ATCAATC</t>
         </is>
       </c>
-      <c r="T58" t="n">
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U58" t="n">
         <v>0.5983606557377049</v>
       </c>
-      <c r="U58" t="n">
+      <c r="V58" t="n">
         <v>0.4016393442622951</v>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -5934,7 +6224,7 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>0.8736</v>
+        <v>0.8907</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
@@ -5964,13 +6254,18 @@
           <t>TGATCACTATCACA</t>
         </is>
       </c>
-      <c r="T59" t="n">
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U59" t="n">
         <v>0.632546981207517</v>
       </c>
-      <c r="U59" t="n">
+      <c r="V59" t="n">
         <v>0.367453018792483</v>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -6026,7 +6321,7 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>0.1845</v>
+        <v>0.2034</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -6060,13 +6355,18 @@
           <t>TGTACAAATGTACA</t>
         </is>
       </c>
-      <c r="T60" t="n">
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U60" t="n">
         <v>0.003798480607756897</v>
       </c>
-      <c r="U60" t="n">
+      <c r="V60" t="n">
         <v>0.9962015193922431</v>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -6122,7 +6422,7 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>0.3529</v>
+        <v>0.4014</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
@@ -6152,13 +6452,18 @@
           <t>GGTGCGCTTCACCGCACC</t>
         </is>
       </c>
-      <c r="T61" t="n">
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U61" t="n">
         <v>0.01239504198320672</v>
       </c>
-      <c r="U61" t="n">
+      <c r="V61" t="n">
         <v>0.9876049580167933</v>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6214,7 +6519,7 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>0.4874</v>
+        <v>0.5153</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -6244,13 +6549,18 @@
           <t>TGTGAACCTCCCCACA</t>
         </is>
       </c>
-      <c r="T62" t="n">
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U62" t="n">
         <v>0.001999200319872051</v>
       </c>
-      <c r="U62" t="n">
+      <c r="V62" t="n">
         <v>0.998000799680128</v>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6306,7 +6616,7 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>0.2345</v>
+        <v>0.2503</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -6340,13 +6650,18 @@
           <t>TTAGTAAAAATACTAA</t>
         </is>
       </c>
-      <c r="T63" t="n">
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U63" t="n">
         <v>0.001399440223910436</v>
       </c>
-      <c r="U63" t="n">
+      <c r="V63" t="n">
         <v>0.9986005597760895</v>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6402,7 +6717,7 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>0.4838</v>
+        <v>0.4917</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -6436,13 +6751,18 @@
           <t>TGTTTAATTATTGTTTAT</t>
         </is>
       </c>
-      <c r="T64" t="n">
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
+      <c r="U64" t="n">
         <v>0.01739304278288685</v>
       </c>
-      <c r="U64" t="n">
+      <c r="V64" t="n">
         <v>0.9826069572171131</v>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6498,7 +6818,7 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>0.5219</v>
+        <v>0.5692</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
@@ -6528,13 +6848,18 @@
           <t>TGTGATTTAGATCACA</t>
         </is>
       </c>
-      <c r="T65" t="n">
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U65" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U65" t="n">
+      <c r="V65" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6590,7 +6915,7 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>0.4234</v>
+        <v>0.436</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -6624,13 +6949,18 @@
           <t>CTGTTTATAATTTGTTTA</t>
         </is>
       </c>
-      <c r="T66" t="n">
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
+      <c r="U66" t="n">
         <v>0.001799280287884846</v>
       </c>
-      <c r="U66" t="n">
+      <c r="V66" t="n">
         <v>0.9982007197121151</v>
       </c>
-      <c r="V66" t="inlineStr">
+      <c r="W66" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6686,7 +7016,7 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>2.2486</v>
+        <v>0.7425</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
@@ -6716,13 +7046,18 @@
           <t>CAAGGTGTTAGATTG</t>
         </is>
       </c>
-      <c r="T67" t="n">
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U67" t="n">
         <v>0.9948020791683326</v>
       </c>
-      <c r="U67" t="n">
+      <c r="V67" t="n">
         <v>0.005197920831667369</v>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -6778,7 +7113,7 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>0.6098</v>
+        <v>0.6181</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
@@ -6808,13 +7143,18 @@
           <t>ATACACTTTGTAACATTT</t>
         </is>
       </c>
-      <c r="T68" t="n">
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
+      <c r="U68" t="n">
         <v>0.04838064774090364</v>
       </c>
-      <c r="U68" t="n">
+      <c r="V68" t="n">
         <v>0.9516193522590963</v>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6870,7 +7210,7 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>0.6469</v>
+        <v>0.6909</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
@@ -6900,13 +7240,18 @@
           <t>CAAAATGTTAA</t>
         </is>
       </c>
-      <c r="T69" t="n">
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U69" t="n">
         <v>0.2990803678528589</v>
       </c>
-      <c r="U69" t="n">
+      <c r="V69" t="n">
         <v>0.7009196321471411</v>
       </c>
-      <c r="V69" t="inlineStr">
+      <c r="W69" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>

--- a/10_Threshold_OUTPUT_REPORT/10_best_conclusion_data.xlsx
+++ b/10_Threshold_OUTPUT_REPORT/10_best_conclusion_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W69"/>
+  <dimension ref="A1:Y69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,55 +491,65 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Used Percentile</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Analysis Note</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>coords</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>length</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>full_pattern</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>evaluation</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>correctness_%</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Inverted_Pval</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Alignment</t>
         </is>
@@ -595,52 +605,58 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.4695</v>
+        <v>0.4714</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
+      <c r="M2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3), (15, 4), (16, 5), (17, 6)]</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>7</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>7.998179496224076</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>GCGAACA</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>GCGAAGA</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>GCGAAGAAAAGGCGAACA</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Ambiguous DR</t>
         </is>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="W2" t="n">
         <v>0.02299080367852859</v>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
         <v>0.9770091963214714</v>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -696,52 +712,58 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.4081</v>
+        <v>0.4095</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="M3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
         <is>
           <t>[(12, 1), (13, 2), (14, 3), (15, 4), (16, 5), (17, 6)]</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>6</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>CGAACA</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>CGAACA</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>CGAACAAAAACCGAACA</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
+        <v>100</v>
+      </c>
+      <c r="W3" t="n">
         <v>0.1105557776889244</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>0.8894442223110756</v>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -797,52 +819,58 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.5138</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
         <is>
           <t>[(11, 6), (12, 7), (13, 8), (14, 9), (15, 10)]</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>5</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>9.999999948007035</v>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>TTGTT</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>TTGTT</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>TTGTTTTGTT</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
+        <v>100</v>
+      </c>
+      <c r="W4" t="n">
         <v>0.6271491403438625</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>0.3728508596561375</v>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -898,52 +926,58 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.2979</v>
+        <v>0.3035</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
+      <c r="M5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>[(7, 6), (8, 5), (9, 4), (10, 3), (11, 2), (12, 1), (13, 0)]</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>7</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>8.158871005219851</v>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>CGAACAT</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>ATGTTCG</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>CGAACATATGTTCG</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
+        <v>100</v>
+      </c>
+      <c r="W5" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -999,48 +1033,54 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.3392</v>
+        <v>0.3342</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
         <is>
           <t>[(8, 6), (9, 5), (10, 4), (11, 3), (12, 2)]</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>5</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>8.877443704354082</v>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>TTACA</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>AGTAA</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>TTACACAGTAA</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Ambiguous IR</t>
         </is>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
+        <v>80</v>
+      </c>
+      <c r="W6" t="n">
         <v>0.06597361055577769</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>0.9340263894442223</v>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -1096,48 +1136,54 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.2653</v>
+        <v>0.2632</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="M7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>[(12, 3), (13, 2), (14, 1), (15, 0)]</t>
         </is>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>7.1887218374957</v>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>CTGT</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>ACAG</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>CTGTTTTTTTATACAG</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
+        <v>100</v>
+      </c>
+      <c r="W7" t="n">
         <v>0.002798880447820872</v>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>0.9972011195521792</v>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1193,52 +1239,58 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.3044</v>
+        <v>0.3036</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>( Caulobacter crescentus NA1000)</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
+      <c r="M8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
         <is>
           <t>[(11, 4), (12, 3), (13, 2), (14, 1)]</t>
         </is>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>4</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>4.649439088043361</v>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>TAAC</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>TTAA</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>TAACGCTCTGTTAA</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Ambiguous IR</t>
         </is>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
+        <v>50</v>
+      </c>
+      <c r="W8" t="n">
         <v>0.03298680527788884</v>
       </c>
-      <c r="V8" t="n">
+      <c r="X8" t="n">
         <v>0.9670131947221111</v>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -1294,48 +1346,54 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.507</v>
+        <v>0.5047</v>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
+      <c r="M9" t="n">
+        <v>10</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
         <is>
           <t>[(12, 1), (13, 2), (14, 3), (15, 4), (16, 5), (17, 6), (18, 7)]</t>
         </is>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>7</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>8.629871735080744</v>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>ATGTTCT</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>ATGTTCT</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>ATGTTCTCGTTATGTTCT</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
+        <v>100</v>
+      </c>
+      <c r="W9" t="n">
         <v>0.0005997600959616154</v>
       </c>
-      <c r="V9" t="n">
+      <c r="X9" t="n">
         <v>0.9994002399040384</v>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1391,52 +1449,58 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.5179</v>
+        <v>0.5235</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>( Caulobacter crescentus NA1000)</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
+      <c r="M10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
         <is>
           <t>[(12, 1), (13, 2), (14, 3), (15, 4), (16, 5)]</t>
         </is>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>5</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>5.644219182897489</v>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>TTAAC</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>TTAAT</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>TTAATGTCCGGTTAAC</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Ambiguous DR</t>
         </is>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
+        <v>80</v>
+      </c>
+      <c r="W10" t="n">
         <v>0.001599360255897641</v>
       </c>
-      <c r="V10" t="n">
+      <c r="X10" t="n">
         <v>0.9984006397441023</v>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1492,48 +1556,54 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0.2588</v>
+        <v>0.2655</v>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
+      <c r="M11" t="n">
+        <v>10</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
         <is>
           <t>[(9, 6), (10, 5), (11, 4), (12, 3), (13, 2), (14, 1), (15, 0)]</t>
         </is>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>7</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>6.018460567146161</v>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>TCGAACA</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>TGTTCGA</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>TCGAACATATGTTCGA</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
+        <v>100</v>
+      </c>
+      <c r="W11" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V11" t="n">
+      <c r="X11" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1589,48 +1659,54 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0.6046</v>
+        <v>0.6623</v>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
+      <c r="M12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
         <is>
           <t>[(15, 4), (16, 3), (17, 2), (18, 1)]</t>
         </is>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>4</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>4.574140548750501</v>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>TGAT</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>ATCA</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>TGATTGTAACTTCGATCA</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
+        <v>100</v>
+      </c>
+      <c r="W12" t="n">
         <v>0.2542982806877249</v>
       </c>
-      <c r="V12" t="n">
+      <c r="X12" t="n">
         <v>0.745701719312275</v>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -1686,48 +1762,54 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0.343</v>
+        <v>0.3433</v>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
+      <c r="M13" t="n">
+        <v>10</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
         <is>
           <t>[(10, 5), (11, 4), (12, 3), (13, 2), (14, 1), (15, 0)]</t>
         </is>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>6</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>5.088423751903059</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>TGTGAT</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>ATCACA</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>TGTGATCTACATCACA</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
+        <v>100</v>
+      </c>
+      <c r="W13" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V13" t="n">
+      <c r="X13" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1783,52 +1865,58 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.2083</v>
+        <v>0.2127</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
+      <c r="M14" t="n">
+        <v>10</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
         <is>
           <t>[(8, 5), (9, 4), (10, 3), (11, 2), (12, 1), (13, 0)]</t>
         </is>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>6</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>AGAACA</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>TGTTCT</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>AGAACAAGTGTTCT</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
+        <v>100</v>
+      </c>
+      <c r="W14" t="n">
         <v>0.005997600959616154</v>
       </c>
-      <c r="V14" t="n">
+      <c r="X14" t="n">
         <v>0.9940023990403839</v>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1884,52 +1972,58 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.2415</v>
+        <v>0.2427</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
+      <c r="M15" t="n">
+        <v>10</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
         <is>
           <t>[(8, 5), (9, 4), (10, 3), (11, 2), (12, 1), (13, 0)]</t>
         </is>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>6</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>10.87744369395549</v>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>AGAACA</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>TGTTCT</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>AGAACAAATGTTCT</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
+        <v>100</v>
+      </c>
+      <c r="W15" t="n">
         <v>0.001399440223910436</v>
       </c>
-      <c r="V15" t="n">
+      <c r="X15" t="n">
         <v>0.9986005597760895</v>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1985,52 +2079,58 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0.3305</v>
+        <v>0.3335</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>[Escherichia coli str. K-12 substr. MG1655]</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="M16" t="n">
+        <v>10</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
         <is>
           <t>[(14, 5), (15, 4), (16, 3), (17, 2), (18, 1), (19, 0)]</t>
         </is>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>6</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>GACTGT</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>ACAGTC</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>GACTGTTTTTTTGTACAGTC</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
+        <v>100</v>
+      </c>
+      <c r="W16" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="V16" t="n">
+      <c r="X16" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2086,52 +2186,58 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0.3921</v>
+        <v>0.3902</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>[Escherichia coli str. K-12 substr. MG1655]</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="M17" t="n">
+        <v>10</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
         <is>
           <t>[(10, 9), (11, 8), (12, 7), (13, 6), (14, 5), (15, 4), (16, 3), (17, 2), (18, 1), (19, 0)]</t>
         </is>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>10</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>9.129186210109001</v>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>TACTGTATTT</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>ATATACAGTA</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>TACTGTATTTATATACAGTA</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Ambiguous IR</t>
         </is>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
+        <v>90</v>
+      </c>
+      <c r="W17" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V17" t="n">
+      <c r="X17" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2187,48 +2293,54 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0.7024</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
+      <c r="M18" t="n">
+        <v>10</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
         <is>
           <t>[(13, 8), (14, 7), (15, 6), (16, 5), (17, 4), (18, 3), (19, 2), (20, 1), (21, 0)]</t>
         </is>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>9</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>7.868062409322926</v>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>TACATTGAG</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>ATCAAAAAA</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>TACATTGAGCAGGATCAAAAAA</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Ambiguous IR</t>
         </is>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="W18" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="V18" t="n">
+      <c r="X18" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2284,48 +2396,54 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0.6017</v>
+        <v>0.6461</v>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
+      <c r="M19" t="n">
+        <v>10</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3), (15, 4), (16, 5), (17, 6)]</t>
         </is>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>7</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>6.712915634015472</v>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>ATGTTAA</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>TTGTTAA</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>TTGTTAAAAAAATGTTAA</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Ambiguous DR</t>
         </is>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="W19" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="V19" t="n">
+      <c r="X19" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2381,48 +2499,54 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0.4949</v>
+        <v>0.4906</v>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
+      <c r="M20" t="n">
+        <v>10</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
         <is>
           <t>[(14, 7), (15, 6), (16, 5), (17, 4), (18, 3)]</t>
         </is>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>5</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>6.230875573321077</v>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>TGTGA</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>TCACA</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>TGTGATCGATATCACA</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
+        <v>100</v>
+      </c>
+      <c r="W20" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V20" t="n">
+      <c r="X20" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2478,52 +2602,58 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>0.9575</v>
+        <v>0.9842</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>(Escherichia coli str. K-12 substr. W3110)</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
+      <c r="M21" t="n">
+        <v>10</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
         <is>
           <t>[(13, 2), (14, 3), (15, 4), (16, 5), (17, 6), (18, 7), (19, 8), (20, 9), (21, 10)]</t>
         </is>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>9</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>6.471313798373604</v>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>TTGTTTATA</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>TTGTTTATA</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>TTGTTTATATTTTGTTTATA</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
+        <v>100</v>
+      </c>
+      <c r="W21" t="n">
         <v>0.0009996001599360256</v>
       </c>
-      <c r="V21" t="n">
+      <c r="X21" t="n">
         <v>0.9990003998400639</v>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2579,52 +2709,58 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>0.4293</v>
+        <v>0.4294</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>(Escherichia coli str. K-12 substr. W3110)</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
+      <c r="M22" t="n">
+        <v>10</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3), (15, 4), (16, 5)]</t>
         </is>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>6</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>8.647947666979002</v>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>TGTTTA</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>TGTTTA</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>TGTTTAGGGTTTGTTTA</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
+        <v>100</v>
+      </c>
+      <c r="W22" t="n">
         <v>0.01079568172730908</v>
       </c>
-      <c r="V22" t="n">
+      <c r="X22" t="n">
         <v>0.989204318272691</v>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2680,52 +2816,58 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>0.3208</v>
+        <v>0.3309</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>(https://www.microbiologyresearch.org/content/journal/micro/10.1099/mic.0.27315-0)</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
+      <c r="M23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
         <is>
           <t>[(12, 3), (13, 2), (14, 1)]</t>
         </is>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>3</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>3.378825754835315</v>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>TGC</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>GCA</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>TGCTCAAAGGGGCA</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
+        <v>100</v>
+      </c>
+      <c r="W23" t="n">
         <v>0.1687325069972011</v>
       </c>
-      <c r="V23" t="n">
+      <c r="X23" t="n">
         <v>0.8312674930027989</v>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -2781,52 +2923,58 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>0.3186</v>
+        <v>0.3245</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
+      <c r="M24" t="n">
+        <v>10</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
         <is>
           <t>[(9, 8), (10, 7), (11, 6), (12, 5), (13, 4), (14, 3), (15, 2), (16, 1), (17, 0)]</t>
         </is>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>9</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>13.50977493180085</v>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>GGTTGACAC</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>ATGTAAACC</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>GGTTGACACATGTAAACC</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>Ambiguous IR</t>
         </is>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
+        <v>77.78</v>
+      </c>
+      <c r="W24" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="V24" t="n">
+      <c r="X24" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2882,48 +3030,54 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>0.3016</v>
+        <v>0.3095</v>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
+      <c r="M25" t="n">
+        <v>10</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
         <is>
           <t>[(10, 5), (11, 4), (12, 3), (13, 2), (14, 1), (15, 0)]</t>
         </is>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>6</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>7.630660794740063</v>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>CTGTAC</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>ATACAG</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>CTGTACATCAATACAG</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>Ambiguous IR</t>
         </is>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="W25" t="n">
         <v>0.002798880447820872</v>
       </c>
-      <c r="V25" t="n">
+      <c r="X25" t="n">
         <v>0.9972011195521792</v>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2979,48 +3133,54 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>0.2934</v>
+        <v>0.2912</v>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
+      <c r="M26" t="n">
+        <v>10</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
         <is>
           <t>[(10, 2), (11, 1), (12, 0)]</t>
         </is>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>3</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>4.845945699069486</v>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>TTT</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>TTTGAAATTCAAA</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
+        <v>100</v>
+      </c>
+      <c r="W26" t="n">
         <v>0.04558176729308277</v>
       </c>
-      <c r="V26" t="n">
+      <c r="X26" t="n">
         <v>0.9544182327069173</v>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3076,52 +3236,58 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>0.2508</v>
+        <v>0.2497</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
+      <c r="M27" t="n">
+        <v>10</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
         <is>
           <t>[(9, 3), (10, 2), (11, 1), (12, 0)]</t>
         </is>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>4</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>7.999999958405628</v>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>TTTG</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>CAAA</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>TTTGCTATACAAA</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
+        <v>100</v>
+      </c>
+      <c r="W27" t="n">
         <v>0.2249100359856057</v>
       </c>
-      <c r="V27" t="n">
+      <c r="X27" t="n">
         <v>0.7750899640143942</v>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3177,48 +3343,54 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0.453</v>
+        <v>0.4531</v>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
+      <c r="M28" t="n">
+        <v>10</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
         <is>
           <t>[(11, 10), (12, 9), (13, 8), (14, 7), (15, 6), (16, 5), (17, 4)]</t>
         </is>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>7</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>8.825779900888758</v>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>AGAACAT</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>ATGTTCG</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>AGAACATATGTTCG</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>Ambiguous IR</t>
         </is>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="W28" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V28" t="n">
+      <c r="X28" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3274,52 +3446,58 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>0.507</v>
+        <v>0.515</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
+      <c r="M29" t="n">
+        <v>10</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
         <is>
           <t>[(9, 8), (10, 7), (11, 6), (12, 5), (13, 4), (14, 3), (15, 2), (16, 1), (17, 0)]</t>
         </is>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>9</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>14.99999991741126</v>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>ACCTAATAA</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>AAATAAGGT</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>ACCTAATAAAAATAAGGT</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>Ambiguous IR</t>
         </is>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="W29" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="V29" t="n">
+      <c r="X29" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3375,52 +3553,58 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0.1819</v>
+        <v>0.1851</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
+      <c r="M30" t="n">
+        <v>10</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
         <is>
           <t>[(7, 4), (8, 3), (9, 2), (10, 1)]</t>
         </is>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>4</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>7.999999958405628</v>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>AACA</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>TGTT</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>AACACATGTT</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
+        <v>100</v>
+      </c>
+      <c r="W30" t="n">
         <v>0.1273490603758497</v>
       </c>
-      <c r="V30" t="n">
+      <c r="X30" t="n">
         <v>0.8726509396241503</v>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3476,52 +3660,58 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0.2188</v>
+        <v>0.2237</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
+      <c r="M31" t="n">
+        <v>10</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
         <is>
           <t>[(7, 4), (8, 3), (9, 2), (10, 1), (11, 0)]</t>
         </is>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>5</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>9.999999948007035</v>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>GAACA</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>TGTTC</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>GAACAGGTGTTC</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
+        <v>100</v>
+      </c>
+      <c r="W31" t="n">
         <v>0.00699720111955218</v>
       </c>
-      <c r="V31" t="n">
+      <c r="X31" t="n">
         <v>0.9930027988804478</v>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3577,52 +3767,58 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>0.2293</v>
+        <v>0.23</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
+      <c r="M32" t="n">
+        <v>10</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
         <is>
           <t>[(9, 6), (10, 5), (11, 4), (12, 3), (13, 2), (14, 1)]</t>
         </is>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>6</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>CGAACA</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>TGTTCG</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>CGAACAGGTGTTCG</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
+        <v>100</v>
+      </c>
+      <c r="W32" t="n">
         <v>0.002399040383846461</v>
       </c>
-      <c r="V32" t="n">
+      <c r="X32" t="n">
         <v>0.9976009596161536</v>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3678,48 +3874,54 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>0.3732</v>
+        <v>0.3772</v>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
+      <c r="M33" t="n">
+        <v>10</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
         <is>
           <t>[(11, 8), (12, 7), (13, 6), (14, 5), (15, 4), (16, 3), (17, 2)]</t>
         </is>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>7</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>10.30104249561152</v>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>TCGAACA</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>TGTTCGA</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>TCGAACACATGTTCGA</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
+        <v>100</v>
+      </c>
+      <c r="W33" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V33" t="n">
+      <c r="X33" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3775,48 +3977,54 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>0.3059</v>
+        <v>0.3614</v>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
+      <c r="M34" t="n">
+        <v>10</v>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
         <is>
           <t>[(9, 6), (10, 5), (11, 4), (12, 3)]</t>
         </is>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>4</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
         <v>4.632331227446766</v>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>AAAG</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>CGTT</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>AAAGCCCGTT</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>Ambiguous IR</t>
         </is>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
+        <v>75</v>
+      </c>
+      <c r="W34" t="n">
         <v>0.7978808476609356</v>
       </c>
-      <c r="V34" t="n">
+      <c r="X34" t="n">
         <v>0.2021191523390644</v>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3872,48 +4080,54 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>0.2857</v>
+        <v>0.2848</v>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
+      <c r="M35" t="n">
+        <v>10</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
         <is>
           <t>[(8, 5), (9, 4), (10, 3), (11, 2), (12, 1), (13, 0)]</t>
         </is>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>6</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>4.649382099447238</v>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>GTATCA</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>TGATAC</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>GTATCATATGATAC</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
+        <v>100</v>
+      </c>
+      <c r="W35" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V35" t="n">
+      <c r="X35" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3969,48 +4183,54 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>0.2591</v>
+        <v>0.2613</v>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
+      <c r="M36" t="n">
+        <v>10</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
         <is>
           <t>[(9, 6), (10, 5), (11, 4), (12, 3), (13, 2), (14, 1), (15, 0)]</t>
         </is>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>7</v>
       </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>7.992602362854127</v>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>TAGTACT</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>TGTACTA</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>TAGTACTTATGTACTA</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>Ambiguous IR</t>
         </is>
       </c>
-      <c r="U36" t="n">
+      <c r="V36" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="W36" t="n">
         <v>0.001999200319872051</v>
       </c>
-      <c r="V36" t="n">
+      <c r="X36" t="n">
         <v>0.998000799680128</v>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -4066,52 +4286,58 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0.3076</v>
+        <v>0.316</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
+      <c r="M37" t="n">
+        <v>10</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3)]</t>
         </is>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>4</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Q37" t="n">
         <v>7.999999958405628</v>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>GAACAACACAGGAAC</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
+        <v>100</v>
+      </c>
+      <c r="W37" t="n">
         <v>0.06517393042782887</v>
       </c>
-      <c r="V37" t="n">
+      <c r="X37" t="n">
         <v>0.9348260695721711</v>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -4167,48 +4393,54 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0.3632</v>
+        <v>0.3637</v>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
+      <c r="M38" t="n">
+        <v>10</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
         <is>
           <t>[(12, 7), (13, 6), (14, 5), (15, 4), (16, 3), (17, 2), (18, 1)]</t>
         </is>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>7</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Q38" t="n">
         <v>8.807992789210587</v>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>ACTGTAT</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>ATACAGT</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>ACTGTATAAATATACAGT</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U38" t="n">
+      <c r="V38" t="n">
+        <v>100</v>
+      </c>
+      <c r="W38" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V38" t="n">
+      <c r="X38" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4264,48 +4496,54 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0.497</v>
+        <v>0.4992</v>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
+      <c r="M39" t="n">
+        <v>10</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3), (15, 4), (16, 5)]</t>
         </is>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>6</v>
       </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
         <v>6.823397644601813</v>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>CTGTCA</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>CTGTCA</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>CTGTCACACAACTGTCA</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
+        <v>100</v>
+      </c>
+      <c r="W39" t="n">
         <v>0.002399040383846461</v>
       </c>
-      <c r="V39" t="n">
+      <c r="X39" t="n">
         <v>0.9976009596161536</v>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4361,48 +4599,54 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0.4527</v>
+        <v>0.4529</v>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
+      <c r="M40" t="n">
+        <v>10</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
         <is>
           <t>[(11, 10), (12, 9), (13, 8), (14, 7), (15, 6), (16, 5), (17, 4), (18, 3)]</t>
         </is>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>8</v>
       </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
         <v>8.833999872781469</v>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>CTGGATAT</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>ATATACAG</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>CTGGATATATATACAG</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>Ambiguous IR</t>
         </is>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="W40" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V40" t="n">
+      <c r="X40" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4458,48 +4702,54 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0.2489</v>
+        <v>0.2944</v>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
+      <c r="M41" t="n">
+        <v>10</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
         <is>
           <t>[(8, 5), (9, 4), (10, 3), (11, 2), (12, 1), (13, 0)]</t>
         </is>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>6</v>
       </c>
-      <c r="P41" t="n">
+      <c r="Q41" t="n">
         <v>8.111705777758363</v>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>TTGATC</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>GATCAA</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>TTGATCCAGATCAA</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
+        <v>100</v>
+      </c>
+      <c r="W41" t="n">
         <v>0.001799280287884846</v>
       </c>
-      <c r="V41" t="n">
+      <c r="X41" t="n">
         <v>0.9982007197121151</v>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4555,52 +4805,58 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>0.3336</v>
+        <v>0.3392</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>(https://pmc.ncbi.nlm.nih.gov/articles/PMC2689224/)</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
+      <c r="M42" t="n">
+        <v>10</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
         <is>
           <t>[(8, 7), (9, 8), (10, 9), (11, 10), (12, 11)]</t>
         </is>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>5</v>
       </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
         <v>9.553371688763029</v>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>TTTTT</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>TTTTT</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>TTTTTT</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
+        <v>100</v>
+      </c>
+      <c r="W42" t="n">
         <v>0.009996001599360257</v>
       </c>
-      <c r="V42" t="n">
+      <c r="X42" t="n">
         <v>0.9900039984006398</v>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4656,52 +4912,58 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0.2659</v>
+        <v>0.2599</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>(?? https://apsjournals.apsnet.org/doi/pdf/10.1094/MPMI-23-7-0927)</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
+      <c r="M43" t="n">
+        <v>10</v>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
         <is>
           <t>[(10, 5), (11, 4), (12, 3), (13, 2), (14, 1), (15, 0)]</t>
         </is>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>6</v>
       </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
         <v>7.668638071329797</v>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>GTATCA</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>GGATAC</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>GTATCACCCCGGATAC</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>Ambiguous IR</t>
         </is>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="W43" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="V43" t="n">
+      <c r="X43" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4757,48 +5019,54 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>0.2805</v>
+        <v>0.2797</v>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
+      <c r="M44" t="n">
+        <v>10</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3)]</t>
         </is>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>4</v>
       </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
         <v>7.42297282353826</v>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>GAACAAGACCGGAAC</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
+        <v>100</v>
+      </c>
+      <c r="W44" t="n">
         <v>0.005597760895641743</v>
       </c>
-      <c r="V44" t="n">
+      <c r="X44" t="n">
         <v>0.9944022391043582</v>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4854,52 +5122,58 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>0.5569</v>
+        <v>0.5622</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
+      <c r="M45" t="n">
+        <v>10</v>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
         <is>
           <t>[(13, 2), (14, 3), (15, 4), (16, 5)]</t>
         </is>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>4</v>
       </c>
-      <c r="P45" t="n">
+      <c r="Q45" t="n">
         <v>7.999999958405628</v>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>GAACACGCGCAGAAC</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
+        <v>100</v>
+      </c>
+      <c r="W45" t="n">
         <v>0.1183526589364254</v>
       </c>
-      <c r="V45" t="n">
+      <c r="X45" t="n">
         <v>0.8816473410635746</v>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -4955,52 +5229,58 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>0.3507</v>
+        <v>0.3536</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
+      <c r="M46" t="n">
+        <v>10</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3)]</t>
         </is>
       </c>
-      <c r="O46" t="n">
+      <c r="P46" t="n">
         <v>4</v>
       </c>
-      <c r="P46" t="n">
+      <c r="Q46" t="n">
         <v>7.999999958405628</v>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>GAACACGCGCAGAAC</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U46" t="n">
+      <c r="V46" t="n">
+        <v>100</v>
+      </c>
+      <c r="W46" t="n">
         <v>0.07217113154738104</v>
       </c>
-      <c r="V46" t="n">
+      <c r="X46" t="n">
         <v>0.9278288684526189</v>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -5056,52 +5336,58 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>0.2848</v>
+        <v>0.2817</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
+      <c r="M47" t="n">
+        <v>10</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
         <is>
           <t>[(8, 6), (9, 5), (10, 4), (11, 3), (12, 2), (13, 1), (14, 0)]</t>
         </is>
       </c>
-      <c r="O47" t="n">
+      <c r="P47" t="n">
         <v>7</v>
       </c>
-      <c r="P47" t="n">
+      <c r="Q47" t="n">
         <v>8.877443698221686</v>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>GAACACA</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>GACGAAC</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>GAACACAGGACGAAC</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>Ambiguous IR</t>
         </is>
       </c>
-      <c r="U47" t="n">
+      <c r="V47" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="W47" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V47" t="n">
+      <c r="X47" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -5157,48 +5443,54 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0.2834</v>
+        <v>0.2915</v>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
+      <c r="M48" t="n">
+        <v>10</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
         <is>
           <t>[(13, 2), (14, 3), (15, 4)]</t>
         </is>
       </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
         <v>3</v>
       </c>
-      <c r="P48" t="n">
+      <c r="Q48" t="n">
         <v>3.485881343809507</v>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>AACGCTCCCGAAAC</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
+        <v>100</v>
+      </c>
+      <c r="W48" t="n">
         <v>0.01599360255897641</v>
       </c>
-      <c r="V48" t="n">
+      <c r="X48" t="n">
         <v>0.9840063974410236</v>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5254,48 +5546,54 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>0.8998</v>
+        <v>0.9082</v>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
+      <c r="M49" t="n">
+        <v>10</v>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
         <is>
           <t>[(14, 3), (15, 4), (16, 5), (17, 6), (18, 7), (19, 8)]</t>
         </is>
       </c>
-      <c r="O49" t="n">
+      <c r="P49" t="n">
         <v>6</v>
       </c>
-      <c r="P49" t="n">
+      <c r="Q49" t="n">
         <v>6.193444837545022</v>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>TGTTTA</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>TGTTTA</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>TGTTTAGATTTTGTTTA</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U49" t="n">
+      <c r="V49" t="n">
+        <v>100</v>
+      </c>
+      <c r="W49" t="n">
         <v>0.0009996001599360256</v>
       </c>
-      <c r="V49" t="n">
+      <c r="X49" t="n">
         <v>0.9990003998400639</v>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5351,48 +5649,54 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>0.283</v>
+        <v>0.2875</v>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
+      <c r="M50" t="n">
+        <v>10</v>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3)]</t>
         </is>
       </c>
-      <c r="O50" t="n">
+      <c r="P50" t="n">
         <v>4</v>
       </c>
-      <c r="P50" t="n">
+      <c r="Q50" t="n">
         <v>5.623842152666399</v>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>GTTA</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>GTTA</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>GTTAATTAAATGTTA</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U50" t="n">
+      <c r="V50" t="n">
+        <v>100</v>
+      </c>
+      <c r="W50" t="n">
         <v>0.1047580967612955</v>
       </c>
-      <c r="V50" t="n">
+      <c r="X50" t="n">
         <v>0.8952419032387046</v>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -5448,48 +5752,54 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>0.2823</v>
+        <v>0.2865</v>
       </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
+      <c r="M51" t="n">
+        <v>10</v>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
         <is>
           <t>[(10, 0), (11, 1), (12, 2), (13, 3), (14, 4), (15, 5)]</t>
         </is>
       </c>
-      <c r="O51" t="n">
+      <c r="P51" t="n">
         <v>6</v>
       </c>
-      <c r="P51" t="n">
+      <c r="Q51" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>TTCATA</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>TTCATA</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>TTCATAATTTTTCATA</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U51" t="n">
+      <c r="V51" t="n">
+        <v>100</v>
+      </c>
+      <c r="W51" t="n">
         <v>0.006197520991603359</v>
       </c>
-      <c r="V51" t="n">
+      <c r="X51" t="n">
         <v>0.9938024790083967</v>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5545,48 +5855,54 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>0.5108</v>
+        <v>0.5069</v>
       </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
+      <c r="M52" t="n">
+        <v>10</v>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
         <is>
           <t>[(12, 1), (13, 2), (14, 3), (15, 4), (16, 5)]</t>
         </is>
       </c>
-      <c r="O52" t="n">
+      <c r="P52" t="n">
         <v>5</v>
       </c>
-      <c r="P52" t="n">
+      <c r="Q52" t="n">
         <v>7.938653979572283</v>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>TGTTC</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>TGTTC</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>TGTTCTTGATTTGTTC</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U52" t="n">
+      <c r="V52" t="n">
+        <v>100</v>
+      </c>
+      <c r="W52" t="n">
         <v>0.02019192323070772</v>
       </c>
-      <c r="V52" t="n">
+      <c r="X52" t="n">
         <v>0.9798080767692923</v>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5642,48 +5958,54 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>0.2362</v>
+        <v>0.2325</v>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
+      <c r="M53" t="n">
+        <v>10</v>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
         <is>
           <t>[(7, 6), (8, 5), (9, 4), (10, 3), (11, 2), (12, 1), (13, 0)]</t>
         </is>
       </c>
-      <c r="O53" t="n">
+      <c r="P53" t="n">
         <v>7</v>
       </c>
-      <c r="P53" t="n">
+      <c r="Q53" t="n">
         <v>8.995593924090324</v>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>CGAACAT</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>ATGTTCG</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>CGAACATATGTTCG</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U53" t="n">
+      <c r="V53" t="n">
+        <v>100</v>
+      </c>
+      <c r="W53" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V53" t="n">
+      <c r="X53" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5739,48 +6061,54 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>0.2589</v>
+        <v>0.2587</v>
       </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
+      <c r="M54" t="n">
+        <v>10</v>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
         <is>
           <t>[(10, 5), (11, 4), (12, 3), (13, 2), (14, 1), (15, 0)]</t>
         </is>
       </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
         <v>6</v>
       </c>
-      <c r="P54" t="n">
+      <c r="Q54" t="n">
         <v>10.31820609521862</v>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>TGTGAT</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>ATCACA</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>TGTGATCAAGATCACA</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U54" t="n">
+      <c r="V54" t="n">
+        <v>100</v>
+      </c>
+      <c r="W54" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V54" t="n">
+      <c r="X54" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5836,48 +6164,54 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>0.6059</v>
+        <v>0.663</v>
       </c>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
+      <c r="M55" t="n">
+        <v>10</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
         <is>
           <t>[(13, 8), (14, 7), (15, 6), (16, 5), (17, 4)]</t>
         </is>
       </c>
-      <c r="O55" t="n">
+      <c r="P55" t="n">
         <v>5</v>
       </c>
-      <c r="P55" t="n">
+      <c r="Q55" t="n">
         <v>5.946157237883602</v>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>GTGAC</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>ATCAC</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>GTGACATAGATCAC</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>Ambiguous IR</t>
         </is>
       </c>
-      <c r="U55" t="n">
+      <c r="V55" t="n">
+        <v>80</v>
+      </c>
+      <c r="W55" t="n">
         <v>0.007796881247501</v>
       </c>
-      <c r="V55" t="n">
+      <c r="X55" t="n">
         <v>0.992203118752499</v>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5933,48 +6267,54 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>0.5124</v>
+        <v>0.5117</v>
       </c>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
+      <c r="M56" t="n">
+        <v>10</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
         <is>
           <t>[(6, 4), (7, 5), (8, 6), (9, 7), (10, 8), (11, 9), (12, 10), (13, 11), (14, 12), (15, 13)]</t>
         </is>
       </c>
-      <c r="O56" t="n">
+      <c r="P56" t="n">
         <v>10</v>
       </c>
-      <c r="P56" t="n">
+      <c r="Q56" t="n">
         <v>9.193695773286672</v>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>TATAAATAAA</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>TGTATAAATA</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>TGTATAAATAAA</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>Ambiguous DR</t>
         </is>
       </c>
-      <c r="U56" t="n">
+      <c r="V56" t="n">
+        <v>60</v>
+      </c>
+      <c r="W56" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="V56" t="n">
+      <c r="X56" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -6030,48 +6370,54 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>0.3152</v>
+        <v>0.3255</v>
       </c>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
+      <c r="M57" t="n">
+        <v>10</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
         <is>
           <t>[(12, 3), (13, 2), (14, 1)]</t>
         </is>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
         <v>3</v>
       </c>
-      <c r="P57" t="n">
+      <c r="Q57" t="n">
         <v>5.999999968804222</v>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>GTG</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>CAC</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>GTGCGCCAAATCAC</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U57" t="n">
+      <c r="V57" t="n">
+        <v>100</v>
+      </c>
+      <c r="W57" t="n">
         <v>0.5715713714514195</v>
       </c>
-      <c r="V57" t="n">
+      <c r="X57" t="n">
         <v>0.4284286285485805</v>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -6127,48 +6473,54 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>0.2264</v>
+        <v>0.2253</v>
       </c>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
+      <c r="M58" t="n">
+        <v>10</v>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
         <is>
           <t>[(10, 6), (11, 7), (12, 8)]</t>
         </is>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
         <v>3</v>
       </c>
-      <c r="P58" t="n">
+      <c r="Q58" t="n">
         <v>5.999999968804222</v>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>ATC</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>ATC</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>ATCAATC</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U58" t="n">
+      <c r="V58" t="n">
+        <v>100</v>
+      </c>
+      <c r="W58" t="n">
         <v>0.5983606557377049</v>
       </c>
-      <c r="V58" t="n">
+      <c r="X58" t="n">
         <v>0.4016393442622951</v>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -6224,48 +6576,54 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>0.8907</v>
+        <v>0.8824</v>
       </c>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
+      <c r="M59" t="n">
+        <v>10</v>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
         <is>
           <t>[(17, 10), (18, 9), (19, 8), (20, 7)]</t>
         </is>
       </c>
-      <c r="O59" t="n">
+      <c r="P59" t="n">
         <v>4</v>
       </c>
-      <c r="P59" t="n">
+      <c r="Q59" t="n">
         <v>1.853855035407096</v>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>TGAT</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>CACA</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>TGATCACTATCACA</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>Ambiguous IR</t>
         </is>
       </c>
-      <c r="U59" t="n">
+      <c r="V59" t="n">
+        <v>50</v>
+      </c>
+      <c r="W59" t="n">
         <v>0.632546981207517</v>
       </c>
-      <c r="V59" t="n">
+      <c r="X59" t="n">
         <v>0.367453018792483</v>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -6321,52 +6679,58 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>0.2034</v>
+        <v>0.2054</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
+      <c r="M60" t="n">
+        <v>10</v>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
         <is>
           <t>[(8, 0), (9, 1), (10, 2), (11, 3), (12, 4), (13, 5)]</t>
         </is>
       </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
         <v>6</v>
       </c>
-      <c r="P60" t="n">
+      <c r="Q60" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>TGTACA</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>TGTACA</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>TGTACAAATGTACA</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U60" t="n">
+      <c r="V60" t="n">
+        <v>100</v>
+      </c>
+      <c r="W60" t="n">
         <v>0.003798480607756897</v>
       </c>
-      <c r="V60" t="n">
+      <c r="X60" t="n">
         <v>0.9962015193922431</v>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -6422,48 +6786,54 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>0.4014</v>
+        <v>0.4038</v>
       </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
+      <c r="M61" t="n">
+        <v>10</v>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
         <is>
           <t>[(15, 8), (16, 7), (17, 6), (18, 5), (19, 4), (20, 3)]</t>
         </is>
       </c>
-      <c r="O61" t="n">
+      <c r="P61" t="n">
         <v>6</v>
       </c>
-      <c r="P61" t="n">
+      <c r="Q61" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>GGTGCG</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>CGCACC</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>GGTGCGCTTCACCGCACC</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U61" t="n">
+      <c r="V61" t="n">
+        <v>100</v>
+      </c>
+      <c r="W61" t="n">
         <v>0.01239504198320672</v>
       </c>
-      <c r="V61" t="n">
+      <c r="X61" t="n">
         <v>0.9876049580167933</v>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6519,48 +6889,54 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>0.5153</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
+      <c r="M62" t="n">
+        <v>10</v>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
         <is>
           <t>[(14, 7), (15, 6), (16, 5), (17, 4), (18, 3)]</t>
         </is>
       </c>
-      <c r="O62" t="n">
+      <c r="P62" t="n">
         <v>5</v>
       </c>
-      <c r="P62" t="n">
+      <c r="Q62" t="n">
         <v>4.559670595665593</v>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>TGTGA</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>CCACA</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>TGTGAACCTCCCCACA</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>Ambiguous IR</t>
         </is>
       </c>
-      <c r="U62" t="n">
+      <c r="V62" t="n">
+        <v>80</v>
+      </c>
+      <c r="W62" t="n">
         <v>0.001999200319872051</v>
       </c>
-      <c r="V62" t="n">
+      <c r="X62" t="n">
         <v>0.998000799680128</v>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6616,52 +6992,58 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>0.2503</v>
+        <v>0.2458</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr">
+      <c r="M63" t="n">
+        <v>10</v>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
         <is>
           <t>[(10, 5), (11, 4), (12, 3), (13, 2), (14, 1), (15, 0)]</t>
         </is>
       </c>
-      <c r="O63" t="n">
+      <c r="P63" t="n">
         <v>6</v>
       </c>
-      <c r="P63" t="n">
+      <c r="Q63" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>TTAGTA</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>TACTAA</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>TTAGTAAAAATACTAA</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U63" t="n">
+      <c r="V63" t="n">
+        <v>100</v>
+      </c>
+      <c r="W63" t="n">
         <v>0.001399440223910436</v>
       </c>
-      <c r="V63" t="n">
+      <c r="X63" t="n">
         <v>0.9986005597760895</v>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6717,52 +7099,58 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>0.4917</v>
+        <v>0.4925</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>(Yersinia pestis KIM10+)</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr">
+      <c r="M64" t="n">
+        <v>10</v>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3), (15, 4), (16, 5), (17, 6)]</t>
         </is>
       </c>
-      <c r="O64" t="n">
+      <c r="P64" t="n">
         <v>7</v>
       </c>
-      <c r="P64" t="n">
+      <c r="Q64" t="n">
         <v>4.956461640427081</v>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>TGTTTAT</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>TGTTTAA</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>TGTTTAATTATTGTTTAT</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>Ambiguous DR</t>
         </is>
       </c>
-      <c r="U64" t="n">
+      <c r="V64" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="W64" t="n">
         <v>0.01739304278288685</v>
       </c>
-      <c r="V64" t="n">
+      <c r="X64" t="n">
         <v>0.9826069572171131</v>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6818,48 +7206,54 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>0.5692</v>
+        <v>0.5698</v>
       </c>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr">
+      <c r="M65" t="n">
+        <v>10</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
         <is>
           <t>[(14, 9), (15, 8), (16, 7), (17, 6), (18, 5), (19, 4)]</t>
         </is>
       </c>
-      <c r="O65" t="n">
+      <c r="P65" t="n">
         <v>6</v>
       </c>
-      <c r="P65" t="n">
+      <c r="Q65" t="n">
         <v>6.726153901717278</v>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>TGTGAT</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>ATCACA</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>TGTGATTTAGATCACA</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U65" t="n">
+      <c r="V65" t="n">
+        <v>100</v>
+      </c>
+      <c r="W65" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V65" t="n">
+      <c r="X65" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6915,52 +7309,58 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>0.436</v>
+        <v>0.4428</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>(Yersinia pestis KIM10+)</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr">
+      <c r="M66" t="n">
+        <v>10</v>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3), (15, 4), (16, 5), (17, 6)]</t>
         </is>
       </c>
-      <c r="O66" t="n">
+      <c r="P66" t="n">
         <v>7</v>
       </c>
-      <c r="P66" t="n">
+      <c r="Q66" t="n">
         <v>6.725409521382448</v>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>TTGTTTA</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>CTGTTTA</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>CTGTTTATAATTTGTTTA</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>Ambiguous DR</t>
         </is>
       </c>
-      <c r="U66" t="n">
+      <c r="V66" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="W66" t="n">
         <v>0.001799280287884846</v>
       </c>
-      <c r="V66" t="n">
+      <c r="X66" t="n">
         <v>0.9982007197121151</v>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -7016,48 +7416,54 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>0.7425</v>
+        <v>0.7346</v>
       </c>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
+      <c r="M67" t="n">
+        <v>10</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
         <is>
           <t>[(14, 4), (15, 3), (16, 2)]</t>
         </is>
       </c>
-      <c r="O67" t="n">
+      <c r="P67" t="n">
         <v>3</v>
       </c>
-      <c r="P67" t="n">
+      <c r="Q67" t="n">
         <v>5.999999968804222</v>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>CAA</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>TTG</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>CAAGGTGTTAGATTG</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U67" t="n">
+      <c r="V67" t="n">
+        <v>100</v>
+      </c>
+      <c r="W67" t="n">
         <v>0.9948020791683326</v>
       </c>
-      <c r="V67" t="n">
+      <c r="X67" t="n">
         <v>0.005197920831667369</v>
       </c>
-      <c r="W67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -7113,48 +7519,54 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>0.6181</v>
+        <v>0.6392</v>
       </c>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr">
+      <c r="M68" t="n">
+        <v>10</v>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
         <is>
           <t>[(11, 1), (12, 2), (13, 3), (14, 4), (15, 5), (16, 6), (17, 7), (18, 8)]</t>
         </is>
       </c>
-      <c r="O68" t="n">
+      <c r="P68" t="n">
         <v>8</v>
       </c>
-      <c r="P68" t="n">
+      <c r="Q68" t="n">
         <v>5.432587976962286</v>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>TAACATTT</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>ATACACTT</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>ATACACTTTGTAACATTT</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>Ambiguous DR</t>
         </is>
       </c>
-      <c r="U68" t="n">
+      <c r="V68" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="W68" t="n">
         <v>0.04838064774090364</v>
       </c>
-      <c r="V68" t="n">
+      <c r="X68" t="n">
         <v>0.9516193522590963</v>
       </c>
-      <c r="W68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -7210,48 +7622,54 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>0.6909</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
+      <c r="M69" t="n">
+        <v>10</v>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
         <is>
           <t>[(14, 12), (15, 11), (16, 10), (17, 9), (18, 8)]</t>
         </is>
       </c>
-      <c r="O69" t="n">
+      <c r="P69" t="n">
         <v>5</v>
       </c>
-      <c r="P69" t="n">
+      <c r="Q69" t="n">
         <v>6.877443711686477</v>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>CAAAA</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>GTTAA</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>CAAAATGTTAA</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>Ambiguous IR</t>
         </is>
       </c>
-      <c r="U69" t="n">
+      <c r="V69" t="n">
+        <v>40</v>
+      </c>
+      <c r="W69" t="n">
         <v>0.2990803678528589</v>
       </c>
-      <c r="V69" t="n">
+      <c r="X69" t="n">
         <v>0.7009196321471411</v>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
